--- a/Drift-changelog.xlsx
+++ b/Drift-changelog.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Changes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Changes'!$A$1:$H$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Changes'!$A$1:$H$123</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -586,7 +586,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every feature, fix and change shipped. 2026-07-07 – 2026-08-28.</t>
+          <t>Every feature, fix and change shipped. 2026-07-07 – 2026-09-11.</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>COUNTA(Changes!E2:E114)</f>
+        <f>COUNTA(Changes!E2:E123)</f>
         <v/>
       </c>
     </row>
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$114,A8)</f>
+        <f>COUNTIF(Changes!$C$2:$C$123,A8)</f>
         <v/>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="E8" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D8)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D8)</f>
         <v/>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="H8" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$114,G8)</f>
+        <f>COUNTIF(Changes!$G$2:$G$123,G8)</f>
         <v/>
       </c>
     </row>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$114,A9)</f>
+        <f>COUNTIF(Changes!$C$2:$C$123,A9)</f>
         <v/>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="E9" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D9)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D9)</f>
         <v/>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="H9" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$114,G9)</f>
+        <f>COUNTIF(Changes!$G$2:$G$123,G9)</f>
         <v/>
       </c>
     </row>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$114,A10)</f>
+        <f>COUNTIF(Changes!$C$2:$C$123,A10)</f>
         <v/>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="E10" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D10)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D10)</f>
         <v/>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="H10" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$114,G10)</f>
+        <f>COUNTIF(Changes!$G$2:$G$123,G10)</f>
         <v/>
       </c>
     </row>
@@ -744,16 +744,16 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$114,A11)</f>
+        <f>COUNTIF(Changes!$C$2:$C$123,A11)</f>
         <v/>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Auth</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="E11" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D11)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D11)</f>
         <v/>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="H11" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$114,G11)</f>
+        <f>COUNTIF(Changes!$G$2:$G$123,G11)</f>
         <v/>
       </c>
     </row>
@@ -773,16 +773,16 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$114,A12)</f>
+        <f>COUNTIF(Changes!$C$2:$C$123,A12)</f>
         <v/>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Auth / Sync</t>
+          <t>Auth</t>
         </is>
       </c>
       <c r="E12" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D12)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D12)</f>
         <v/>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="H12" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$114,G12)</f>
+        <f>COUNTIF(Changes!$G$2:$G$123,G12)</f>
         <v/>
       </c>
     </row>
@@ -802,16 +802,16 @@
         </is>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$114,A13)</f>
+        <f>COUNTIF(Changes!$C$2:$C$123,A13)</f>
         <v/>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Auth / Sync</t>
         </is>
       </c>
       <c r="E13" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D13)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D13)</f>
         <v/>
       </c>
       <c r="G13" s="7" t="inlineStr">
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="H13" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$114,G13)</f>
+        <f>COUNTIF(Changes!$G$2:$G$123,G13)</f>
         <v/>
       </c>
     </row>
@@ -831,346 +831,390 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$114,A14)</f>
+        <f>COUNTIF(Changes!$C$2:$C$123,A14)</f>
         <v/>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Billing</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="E14" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D14)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>CI/CD</t>
+          <t>Billing</t>
         </is>
       </c>
       <c r="E15" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D15)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>CI/CD</t>
         </is>
       </c>
       <c r="E16" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D16)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Challenges</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E17" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D17)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Dependencies</t>
+          <t>Challenges</t>
         </is>
       </c>
       <c r="E18" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D18)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Discoverability</t>
+          <t>Dependencies</t>
         </is>
       </c>
       <c r="E19" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D19)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Drift In</t>
+          <t>Discoverability</t>
         </is>
       </c>
       <c r="E20" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D20)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>Drift In</t>
         </is>
       </c>
       <c r="E21" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D21)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Family</t>
         </is>
       </c>
       <c r="E22" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D22)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Interaction</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="E23" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D23)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D23)</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Navigation</t>
+          <t>Infra</t>
         </is>
       </c>
       <c r="E24" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D24)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Interaction</t>
         </is>
       </c>
       <c r="E25" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D25)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Lockbox</t>
         </is>
       </c>
       <c r="E26" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D26)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Payments</t>
+          <t>Navigation</t>
         </is>
       </c>
       <c r="E27" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D27)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D27)</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="E28" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D28)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="E29" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D29)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Payments</t>
         </is>
       </c>
       <c r="E30" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D30)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Release</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E31" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D31)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Scaling</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="E32" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D32)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Screen Time</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D33)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Release</t>
         </is>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D34)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D34)</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Siri</t>
+          <t>Scaling</t>
         </is>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D35)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D35)</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Sleep Guard</t>
+          <t>Screen Time</t>
         </is>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D36)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D36)</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Tasks</t>
+          <t>Shield</t>
         </is>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D37)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D37)</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Theme</t>
+          <t>Siri</t>
         </is>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D38)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D38)</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Tour</t>
+          <t>Sleep Guard</t>
         </is>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D39)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D39)</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Tasks</t>
         </is>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D40)</f>
+        <f>COUNTIF(Changes!$D$2:$D$123,D40)</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="D41" s="7" t="inlineStr">
         <is>
+          <t>Theme</t>
+        </is>
+      </c>
+      <c r="E41" s="7">
+        <f>COUNTIF(Changes!$D$2:$D$123,D41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Tour</t>
+        </is>
+      </c>
+      <c r="E42" s="7">
+        <f>COUNTIF(Changes!$D$2:$D$123,D42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="E43" s="7">
+        <f>COUNTIF(Changes!$D$2:$D$123,D43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Updates</t>
+        </is>
+      </c>
+      <c r="E44" s="7">
+        <f>COUNTIF(Changes!$D$2:$D$123,D44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="D45" s="7" t="inlineStr">
+        <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="E41" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D41)</f>
+      <c r="E45" s="7">
+        <f>COUNTIF(Changes!$D$2:$D$123,D45)</f>
         <v/>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="13" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="13" t="inlineStr">
         <is>
           <t>• 1.1.4 is the last version submitted to the App Store. Everything marked Unreleased is on main but not shipped.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="13" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
         <is>
           <t>• "Needs" says what a change requires beyond a normal JS reload: a native rebuild, an edge-function deploy, or SQL run in Supabase.</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="13" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="13" t="inlineStr">
         <is>
           <t>• Native-build items are currently blocked on Apple Developer account access, so they are not device-tested.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="13" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="13" t="inlineStr">
         <is>
           <t>• Counts on this sheet are formulas over the Changes tab — they update if you edit, add or delete rows there.</t>
         </is>
@@ -1187,7 +1231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H114"/>
+  <dimension ref="A1:H123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -5980,8 +6024,386 @@
         </is>
       </c>
     </row>
+    <row r="115" ht="40" customHeight="1">
+      <c r="A115" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B115" s="16" t="inlineStr">
+        <is>
+          <t>dcaf805</t>
+        </is>
+      </c>
+      <c r="C115" s="17" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D115" s="15" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="E115" s="18" t="inlineStr">
+        <is>
+          <t>Drift runs on Android</t>
+        </is>
+      </c>
+      <c r="F115" s="18" t="inlineStr">
+        <is>
+          <t>Native project generated and committed alongside ios/. All four Android icons are derived from the single iOS app icon by tools/build-android-icons.js so there is one source of truth - the notification icon has to be a white silhouette because Android discards colour and keeps only the alpha channel, and a coloured one renders as a white blob. Four notification channels replace the single bucket expo-notifications would otherwise invent, so muting the daily streak nudge no longer also mutes a lockbox breach warning.</t>
+        </is>
+      </c>
+      <c r="G115" s="25" t="inlineStr">
+        <is>
+          <t>Unreleased</t>
+        </is>
+      </c>
+      <c r="H115" s="22" t="inlineStr">
+        <is>
+          <t>Native build</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="40" customHeight="1">
+      <c r="A116" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B116" s="16" t="inlineStr">
+        <is>
+          <t>afe45b5</t>
+        </is>
+      </c>
+      <c r="C116" s="17" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D116" s="15" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="E116" s="18" t="inlineStr">
+        <is>
+          <t>App blocking on Android, without Family Controls</t>
+        </is>
+      </c>
+      <c r="F116" s="18" t="inlineStr">
+        <is>
+          <t>Android exposes no API for one app to shield another, so Drift does it itself: a foreground service polling UsageStatsManager at 1Hz, an optional AccessibilityService for instant detection, and a full ShieldActivity - an activity rather than a floating overlay, so the blocked app is paused by the OS instead of left playing underneath. Built as a local Expo module so `expo prebuild --clean` cannot wipe it. The JS interface mirrors iOS ScreenTimeModule exactly, so Drift In, blocked hours and the balance reconcile drive it through calls they already made and no screen needed rewriting. Verified on device, including after a reboot with Drift never opened.</t>
+        </is>
+      </c>
+      <c r="G116" s="25" t="inlineStr">
+        <is>
+          <t>Unreleased</t>
+        </is>
+      </c>
+      <c r="H116" s="22" t="inlineStr">
+        <is>
+          <t>Native build</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="40" customHeight="1">
+      <c r="A117" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B117" s="16" t="inlineStr">
+        <is>
+          <t>ef7d882</t>
+        </is>
+      </c>
+      <c r="C117" s="19" t="inlineStr">
+        <is>
+          <t>Bug Fix</t>
+        </is>
+      </c>
+      <c r="D117" s="15" t="inlineStr">
+        <is>
+          <t>Lockbox</t>
+        </is>
+      </c>
+      <c r="E117" s="18" t="inlineStr">
+        <is>
+          <t>Lockbox handed out screen time without ever checking the phone (Android)</t>
+        </is>
+      </c>
+      <c r="F117" s="18" t="inlineStr">
+        <is>
+          <t>startMonitoring() threw "unavailable" on Android and every call site swallowed it, and onStateChange() returned a no-op - so markDisturbed(), the only route to forfeiting a session, could never fire. Every session ran to settle("completed") and awarded the full reward whether or not the phone went in the box: start a 90-minute session, use the phone throughout, collect 45 minutes. Fixed by porting the iOS motion sensing to SensorManager with the constants copied rather than re-tuned. One real difference: both platforms point z out through the screen but disagree on the sign, so Android tests gravity.z &gt; +0.8g for face-up where iOS tests &lt; -0.8.</t>
+        </is>
+      </c>
+      <c r="G117" s="25" t="inlineStr">
+        <is>
+          <t>Unreleased</t>
+        </is>
+      </c>
+      <c r="H117" s="22" t="inlineStr">
+        <is>
+          <t>Native build</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="40" customHeight="1">
+      <c r="A118" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B118" s="16" t="inlineStr">
+        <is>
+          <t>0e939db</t>
+        </is>
+      </c>
+      <c r="C118" s="19" t="inlineStr">
+        <is>
+          <t>Bug Fix</t>
+        </is>
+      </c>
+      <c r="D118" s="15" t="inlineStr">
+        <is>
+          <t>Screen Time</t>
+        </is>
+      </c>
+      <c r="E118" s="18" t="inlineStr">
+        <is>
+          <t>Screen-time sync had been failing for every user on both platforms</t>
+        </is>
+      </c>
+      <c r="F118" s="18" t="inlineStr">
+        <is>
+          <t>syncScreenTime warned 'record new has no field updated_at' on every call. schema_v7 declared the column inside `create table IF NOT EXISTS public.screen_time`, but the table already existed from schema_v2, so the whole CREATE was skipped and the column never landed; spent_minutes survived only because it got its own explicit ALTER afterwards. The trigger referencing it was created unconditionally and has thrown ever since. Because the upsert conflicts on (user_id, date), the first write each day INSERTed and succeeded while every later write UPDATEd and failed - which is why the friends leaderboard showed stale screen time rather than none. Confirmed with a PostgREST probe (42703 before, 200 after) rather than from the push output.</t>
+        </is>
+      </c>
+      <c r="G118" s="25" t="inlineStr">
+        <is>
+          <t>Unreleased</t>
+        </is>
+      </c>
+      <c r="H118" s="22" t="inlineStr">
+        <is>
+          <t>SQL migration</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="40" customHeight="1">
+      <c r="A119" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B119" s="16" t="inlineStr">
+        <is>
+          <t>4042b4c</t>
+        </is>
+      </c>
+      <c r="C119" s="19" t="inlineStr">
+        <is>
+          <t>Bug Fix</t>
+        </is>
+      </c>
+      <c r="D119" s="15" t="inlineStr">
+        <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="E119" s="18" t="inlineStr">
+        <is>
+          <t>expo-constants was pinned four SDKs ahead of the project</t>
+        </is>
+      </c>
+      <c r="F119" s="18" t="inlineStr">
+        <is>
+          <t>package.json carried expo-constants ^57.0.8 against Expo SDK 54, which expects ~18.0.14 - the only expo-* dependency using a caret. iOS tolerated it; Android would not compile at all, because that version calls expo.modules.kotlin.services.ServiceInterface, which does not exist in SDK 54 expo-modules-core. react-native-svg was also behind and aborted the process during Fabric component registration before a single frame rendered.</t>
+        </is>
+      </c>
+      <c r="G119" s="25" t="inlineStr">
+        <is>
+          <t>Unreleased</t>
+        </is>
+      </c>
+      <c r="H119" s="22" t="inlineStr">
+        <is>
+          <t>Native build</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="40" customHeight="1">
+      <c r="A120" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B120" s="16" t="inlineStr">
+        <is>
+          <t>82407e9</t>
+        </is>
+      </c>
+      <c r="C120" s="19" t="inlineStr">
+        <is>
+          <t>Bug Fix</t>
+        </is>
+      </c>
+      <c r="D120" s="15" t="inlineStr">
+        <is>
+          <t>Updates</t>
+        </is>
+      </c>
+      <c r="E120" s="18" t="inlineStr">
+        <is>
+          <t>The force-update gate would have locked out every Android install</t>
+        </is>
+      </c>
+      <c r="F120" s="18" t="inlineStr">
+        <is>
+          <t>Check 2 read app_config.min_ios_version with no platform guard, while checks 1 and 3 were iOS-gated. Setting that key for an iOS hotfix would have caught every Android install too and held it behind ForceUpdateModal - which has no dismiss - pointed at an App Store URL it cannot install from. The same class of lockout as 2026-07-29, arriving from a config row instead of a stale app.json. All four keys are now per-store, and the Android ones do not exist yet, so Android is inert by default.</t>
+        </is>
+      </c>
+      <c r="G120" s="25" t="inlineStr">
+        <is>
+          <t>Unreleased</t>
+        </is>
+      </c>
+      <c r="H120" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="40" customHeight="1">
+      <c r="A121" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B121" s="16" t="inlineStr">
+        <is>
+          <t>afe45b5</t>
+        </is>
+      </c>
+      <c r="C121" s="19" t="inlineStr">
+        <is>
+          <t>Bug Fix</t>
+        </is>
+      </c>
+      <c r="D121" s="15" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="E121" s="18" t="inlineStr">
+        <is>
+          <t>Blocking would have worked in every dev build and died in production</t>
+        </is>
+      </c>
+      <c r="F121" s="18" t="inlineStr">
+        <is>
+          <t>SYSTEM_ALERT_WINDOW sat in blockedPermissions from when it looked unused. React Native declares it independently in the debug manifest for the dev overlay, so it was present in every debug build and stripped from release - canDrawOverlays() would have returned false forever, the shield would never have launched, and the permission would not even have appeared in Settings for the user to grant. Caught by diffing the merged debug and release manifests, which is now worth doing before any submission.</t>
+        </is>
+      </c>
+      <c r="G121" s="25" t="inlineStr">
+        <is>
+          <t>Unreleased</t>
+        </is>
+      </c>
+      <c r="H121" s="22" t="inlineStr">
+        <is>
+          <t>Native build</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="40" customHeight="1">
+      <c r="A122" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B122" s="16" t="inlineStr">
+        <is>
+          <t>603c608</t>
+        </is>
+      </c>
+      <c r="C122" s="19" t="inlineStr">
+        <is>
+          <t>Bug Fix</t>
+        </is>
+      </c>
+      <c r="D122" s="15" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="E122" s="18" t="inlineStr">
+        <is>
+          <t>Calendar sync silently refused to turn on</t>
+        </is>
+      </c>
+      <c r="F122" s="18" t="inlineStr">
+        <is>
+          <t>The toggle flipped on and immediately back off, with no dialog and no error. expo-calendar requests READ_CALENDAR and WRITE_CALENDAR together and gates on hasGrantedPermissions(READ, WRITE) - both - but WRITE was in blockedPermissions, so it could never be granted and toggleCalendar() reverted itself. Drift still never writes to a calendar; the permission is held only because the expo-calendar gate demands it. WRITE_CONTACTS stays blocked, because expo-contacts checks isPermissionPresentInManifest first and asks for READ alone when it is absent.</t>
+        </is>
+      </c>
+      <c r="G122" s="25" t="inlineStr">
+        <is>
+          <t>Unreleased</t>
+        </is>
+      </c>
+      <c r="H122" s="22" t="inlineStr">
+        <is>
+          <t>Native build</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B123" s="16" t="inlineStr">
+        <is>
+          <t>dcaf805</t>
+        </is>
+      </c>
+      <c r="C123" s="19" t="inlineStr">
+        <is>
+          <t>Bug Fix</t>
+        </is>
+      </c>
+      <c r="D123" s="15" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="E123" s="18" t="inlineStr">
+        <is>
+          <t>Android users would have hit a paywall they could not buy through</t>
+        </is>
+      </c>
+      <c r="F123" s="18" t="inlineStr">
+        <is>
+          <t>RevenueCat issues one public SDK key per store and they are not interchangeable, but every non-iOS caller got "not_ios" and failed closed. Now platform-selected via EXPO_PUBLIC_RC_ANDROID_KEY, deliberately with no hardcoded fallback: the 2026-08-28 note in that file records a stale hardcoded key outliving its app and shipping silently in every build, because a wrong key fails exactly like a missing one except a missing one says so.</t>
+        </is>
+      </c>
+      <c r="G123" s="25" t="inlineStr">
+        <is>
+          <t>Unreleased</t>
+        </is>
+      </c>
+      <c r="H123" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H114"/>
+  <autoFilter ref="A1:H123"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Drift-changelog.xlsx
+++ b/Drift-changelog.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Changes'!$A$1:$H$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Changes'!$A$1:$H$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -586,7 +586,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every feature, fix and change shipped. 2026-07-07 – 2026-08-28.</t>
+          <t>Every feature, fix and change shipped. 2026-07-07 – 2026-09-11.</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>COUNTA(Changes!E2:E114)</f>
+        <f>COUNTA(Changes!E2:E127)</f>
         <v/>
       </c>
     </row>
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$114,A8)</f>
+        <f>COUNTIF(Changes!$C$2:$C$127,A8)</f>
         <v/>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="E8" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D8)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D8)</f>
         <v/>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="H8" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$114,G8)</f>
+        <f>COUNTIF(Changes!$G$2:$G$127,G8)</f>
         <v/>
       </c>
     </row>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$114,A9)</f>
+        <f>COUNTIF(Changes!$C$2:$C$127,A9)</f>
         <v/>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="E9" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D9)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D9)</f>
         <v/>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="H9" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$114,G9)</f>
+        <f>COUNTIF(Changes!$G$2:$G$127,G9)</f>
         <v/>
       </c>
     </row>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$114,A10)</f>
+        <f>COUNTIF(Changes!$C$2:$C$127,A10)</f>
         <v/>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="E10" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D10)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D10)</f>
         <v/>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="H10" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$114,G10)</f>
+        <f>COUNTIF(Changes!$G$2:$G$127,G10)</f>
         <v/>
       </c>
     </row>
@@ -744,16 +744,16 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$114,A11)</f>
+        <f>COUNTIF(Changes!$C$2:$C$127,A11)</f>
         <v/>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Auth</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="E11" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D11)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D11)</f>
         <v/>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="H11" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$114,G11)</f>
+        <f>COUNTIF(Changes!$G$2:$G$127,G11)</f>
         <v/>
       </c>
     </row>
@@ -773,16 +773,16 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$114,A12)</f>
+        <f>COUNTIF(Changes!$C$2:$C$127,A12)</f>
         <v/>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Auth / Sync</t>
+          <t>Auth</t>
         </is>
       </c>
       <c r="E12" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D12)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D12)</f>
         <v/>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="H12" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$114,G12)</f>
+        <f>COUNTIF(Changes!$G$2:$G$127,G12)</f>
         <v/>
       </c>
     </row>
@@ -802,16 +802,16 @@
         </is>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$114,A13)</f>
+        <f>COUNTIF(Changes!$C$2:$C$127,A13)</f>
         <v/>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Auth / Sync</t>
         </is>
       </c>
       <c r="E13" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D13)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D13)</f>
         <v/>
       </c>
       <c r="G13" s="7" t="inlineStr">
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="H13" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$114,G13)</f>
+        <f>COUNTIF(Changes!$G$2:$G$127,G13)</f>
         <v/>
       </c>
     </row>
@@ -831,346 +831,423 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$114,A14)</f>
+        <f>COUNTIF(Changes!$C$2:$C$127,A14)</f>
         <v/>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Billing</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="E14" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D14)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>CI/CD</t>
+          <t>Billing</t>
         </is>
       </c>
       <c r="E15" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D15)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>CI/CD</t>
         </is>
       </c>
       <c r="E16" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D16)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Challenges</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E17" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D17)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Dependencies</t>
+          <t>Challenges</t>
         </is>
       </c>
       <c r="E18" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D18)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Discoverability</t>
+          <t>Dependencies</t>
         </is>
       </c>
       <c r="E19" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D19)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Drift In</t>
+          <t>Discoverability</t>
         </is>
       </c>
       <c r="E20" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D20)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>Drift In</t>
         </is>
       </c>
       <c r="E21" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D21)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Entitlement</t>
         </is>
       </c>
       <c r="E22" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D22)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Interaction</t>
+          <t>Family</t>
         </is>
       </c>
       <c r="E23" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D23)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D23)</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Navigation</t>
+          <t>Force update</t>
         </is>
       </c>
       <c r="E24" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D24)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="E25" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D25)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Interaction</t>
         </is>
       </c>
       <c r="E26" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D26)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Payments</t>
+          <t>Lockbox</t>
         </is>
       </c>
       <c r="E27" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D27)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D27)</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Navigation</t>
         </is>
       </c>
       <c r="E28" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D28)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="E29" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D29)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="E30" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D30)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Release</t>
+          <t>Payments</t>
         </is>
       </c>
       <c r="E31" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D31)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Scaling</t>
+          <t>Paywall</t>
         </is>
       </c>
       <c r="E32" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D32)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Screen Time</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D33)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D34)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D34)</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Siri</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D35)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D35)</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Sleep Guard</t>
+          <t>Release</t>
         </is>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D36)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D36)</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Tasks</t>
+          <t>Reviews</t>
         </is>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D37)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D37)</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Theme</t>
+          <t>Scaling</t>
         </is>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D38)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D38)</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Tour</t>
+          <t>Screen Time</t>
         </is>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D39)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D39)</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Shield</t>
         </is>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D40)</f>
+        <f>COUNTIF(Changes!$D$2:$D$127,D40)</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="D41" s="7" t="inlineStr">
         <is>
+          <t>Siri</t>
+        </is>
+      </c>
+      <c r="E41" s="7">
+        <f>COUNTIF(Changes!$D$2:$D$127,D41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Sleep Guard</t>
+        </is>
+      </c>
+      <c r="E42" s="7">
+        <f>COUNTIF(Changes!$D$2:$D$127,D42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="E43" s="7">
+        <f>COUNTIF(Changes!$D$2:$D$127,D43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Tasks</t>
+        </is>
+      </c>
+      <c r="E44" s="7">
+        <f>COUNTIF(Changes!$D$2:$D$127,D44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Theme</t>
+        </is>
+      </c>
+      <c r="E45" s="7">
+        <f>COUNTIF(Changes!$D$2:$D$127,D45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Tour</t>
+        </is>
+      </c>
+      <c r="E46" s="7">
+        <f>COUNTIF(Changes!$D$2:$D$127,D46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="E47" s="7">
+        <f>COUNTIF(Changes!$D$2:$D$127,D47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="D48" s="7" t="inlineStr">
+        <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="E41" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$114,D41)</f>
+      <c r="E48" s="7">
+        <f>COUNTIF(Changes!$D$2:$D$127,D48)</f>
         <v/>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="13" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="13" t="inlineStr">
         <is>
           <t>• 1.1.4 is the last version submitted to the App Store. Everything marked Unreleased is on main but not shipped.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="13" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="13" t="inlineStr">
         <is>
           <t>• "Needs" says what a change requires beyond a normal JS reload: a native rebuild, an edge-function deploy, or SQL run in Supabase.</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="13" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="13" t="inlineStr">
         <is>
           <t>• Native-build items are currently blocked on Apple Developer account access, so they are not device-tested.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="13" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="13" t="inlineStr">
         <is>
           <t>• Counts on this sheet are formulas over the Changes tab — they update if you edit, add or delete rows there.</t>
         </is>
@@ -1187,7 +1264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H114"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -5980,8 +6057,554 @@
         </is>
       </c>
     </row>
+    <row r="115" ht="40" customHeight="1">
+      <c r="A115" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B115" s="16" t="inlineStr">
+        <is>
+          <t>97150ce</t>
+        </is>
+      </c>
+      <c r="C115" s="17" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D115" s="15" t="inlineStr">
+        <is>
+          <t>Lockbox</t>
+        </is>
+      </c>
+      <c r="E115" s="18" t="inlineStr">
+        <is>
+          <t>Put the phone in an AR box, and a session runs until it comes out</t>
+        </is>
+      </c>
+      <c r="F115" s="18" t="inlineStr">
+        <is>
+          <t>Drift In gains a Lockbox mode: place a box on a real surface through ARKit (a lit cage with a live preview that follows the surface), set the phone inside screen up, and the session starts itself when the phone is flat and still. CoreMotion watches for the phone leaving; a 5-second grace window, then the session is lost. Leaving the app is treated exactly as lifting the phone - iOS gives an app no way to block the home swipe, so the countdown follows the user out as a scheduled notification rather than ticking on a screen they cannot see. A lock-seal animation marks the start. Ten commits through 6a11773; the fixes among them (camera left running at placement, a stale closure pinning every session to 25 minutes, an AR error that started a session with no box) never shipped.</t>
+        </is>
+      </c>
+      <c r="G115" s="16" t="inlineStr">
+        <is>
+          <t>1.1.7</t>
+        </is>
+      </c>
+      <c r="H115" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="40" customHeight="1">
+      <c r="A116" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B116" s="16" t="inlineStr">
+        <is>
+          <t>90fa7e1</t>
+        </is>
+      </c>
+      <c r="C116" s="17" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D116" s="15" t="inlineStr">
+        <is>
+          <t>Entitlement</t>
+        </is>
+      </c>
+      <c r="E116" s="18" t="inlineStr">
+        <is>
+          <t>Cohort redemption codes for partner programmes</t>
+        </is>
+      </c>
+      <c r="F116" s="18" t="inlineStr">
+        <is>
+          <t>Codes tied to a named cohort with a per-code grant length, for the Johns Hopkins teen study (50 days from each redemption). Extends schema_v10's redeem_codes rather than building beside it, and grants through pro_overrides so is_pro() needed no change. redeem_cohort_code() does the whole redemption under a row lock - the edge function's read-modify-write on uses let two people take the last seat of a capped code. Never shortens an existing grant. Adds email verification and per-user/per-IP rate limits the function lacked, and revokes the RPC from clients (it takes the uid as a parameter). Entry point is a quiet 'Have a cohort code?' on the paywall, the only screen a non-subscriber can reach. cohort_report() gives redemption counts for the research team. Includes 04a5c37: the confirmation sheet was torn down with the paywall before it could paint.</t>
+        </is>
+      </c>
+      <c r="G116" s="16" t="inlineStr">
+        <is>
+          <t>1.1.7</t>
+        </is>
+      </c>
+      <c r="H116" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="40" customHeight="1">
+      <c r="A117" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B117" s="16" t="inlineStr">
+        <is>
+          <t>79182e1</t>
+        </is>
+      </c>
+      <c r="C117" s="24" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D117" s="15" t="inlineStr">
+        <is>
+          <t>Entitlement</t>
+        </is>
+      </c>
+      <c r="E117" s="18" t="inlineStr">
+        <is>
+          <t>Server-side Pro gating is back, behind a database switch</t>
+        </is>
+      </c>
+      <c r="F117" s="18" t="inlineStr">
+        <is>
+          <t>verify-task and evaluate-task computed whether the caller was Pro and discarded the answer - the 402 was commented out until Apple IAP was re-enabled. It now fires when app_config.enforce_pro_gating = 'true', flipped in the SQL editor with no deploy either way. Read only for unentitled callers, cached 60s; a failed read keeps the last value seen. Switched ON 2026-09-19 after the Paid Apps agreement went active.</t>
+        </is>
+      </c>
+      <c r="G117" s="16" t="inlineStr">
+        <is>
+          <t>1.1.7</t>
+        </is>
+      </c>
+      <c r="H117" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="40" customHeight="1">
+      <c r="A118" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B118" s="16" t="inlineStr">
+        <is>
+          <t>802836b</t>
+        </is>
+      </c>
+      <c r="C118" s="19" t="inlineStr">
+        <is>
+          <t>Bug Fix</t>
+        </is>
+      </c>
+      <c r="D118" s="15" t="inlineStr">
+        <is>
+          <t>Payments</t>
+        </is>
+      </c>
+      <c r="E118" s="18" t="inlineStr">
+        <is>
+          <t>Purchases by customers with an anonymous RevenueCat id never reached the server</t>
+        </is>
+      </c>
+      <c r="F118" s="18" t="inlineStr">
+        <is>
+          <t>revenuecat-webhook dropped any event whose app_user_id was an $RCAnonymousID and returned 200, so RevenueCat never retried. RevenueCat defines app_user_id as the LAST-SEEN id, and a customer who first opened Drift signed out carries their Supabase id only as an alias - Riaan's own record is exactly that shape. With gating on, such a payer would have been refused AI Check. The account is now resolved across app_user_id, original_app_user_id and aliases. Also fixed: an update matching no profile reported success.</t>
+        </is>
+      </c>
+      <c r="G118" s="16" t="inlineStr">
+        <is>
+          <t>1.1.7</t>
+        </is>
+      </c>
+      <c r="H118" s="22" t="inlineStr">
+        <is>
+          <t>First real purchase end-to-end not yet observed</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="40" customHeight="1">
+      <c r="A119" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B119" s="16" t="inlineStr">
+        <is>
+          <t>0ac6369</t>
+        </is>
+      </c>
+      <c r="C119" s="19" t="inlineStr">
+        <is>
+          <t>Bug Fix</t>
+        </is>
+      </c>
+      <c r="D119" s="15" t="inlineStr">
+        <is>
+          <t>Paywall</t>
+        </is>
+      </c>
+      <c r="E119" s="18" t="inlineStr">
+        <is>
+          <t>Free trial advertised to people who had already used it</t>
+        </is>
+      </c>
+      <c r="F119" s="18" t="inlineStr">
+        <is>
+          <t>The paywall read the trial length off the PRODUCT and never asked whether the PERSON was eligible; checkTrialOrIntroductoryPriceEligibility was called nowhere. Someone who had trialled and cancelled saw 'START MY 7 FREE DAYS' and was charged immediately. Now fails closed per RevenueCat's guidance: only ELIGIBLE shows a trial. Also removed trialDays || FALLBACK_TRIAL_DAYS, which promised seven days whenever a product had no intro offer at all. An App Store 3.1.2 risk as well as a trust one.</t>
+        </is>
+      </c>
+      <c r="G119" s="16" t="inlineStr">
+        <is>
+          <t>1.1.7</t>
+        </is>
+      </c>
+      <c r="H119" s="22" t="inlineStr">
+        <is>
+          <t>Ineligible-tester sandbox check not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="40" customHeight="1">
+      <c r="A120" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B120" s="16" t="inlineStr">
+        <is>
+          <t>16b1e2d</t>
+        </is>
+      </c>
+      <c r="C120" s="17" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D120" s="15" t="inlineStr">
+        <is>
+          <t>Reviews</t>
+        </is>
+      </c>
+      <c r="E120" s="18" t="inlineStr">
+        <is>
+          <t>Ask for a review up to three times a year, and never for five stars</t>
+        </is>
+      </c>
+      <c r="F120" s="18" t="inlineStr">
+        <is>
+          <t>Drift asked once ever, after the third task, spending one of Apple's three yearly prompts and discarding the rest. reviewPrompt.js now allows three asks in a rolling year, 90+ days apart - Apple's throttle is silent, so a second ask inside a week is simply wasted. Adds a trigger after a completed focus or Lockbox session. Copy changed from 'A 5-star review' to 'A review': Apple permits asking for a review, not a rating, and the app was rejected once already over prompting (5.6.3).</t>
+        </is>
+      </c>
+      <c r="G120" s="16" t="inlineStr">
+        <is>
+          <t>1.1.7</t>
+        </is>
+      </c>
+      <c r="H120" s="22" t="inlineStr">
+        <is>
+          <t>Prompt only displays in App Store builds</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="40" customHeight="1">
+      <c r="A121" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B121" s="16" t="inlineStr">
+        <is>
+          <t>c79f41c</t>
+        </is>
+      </c>
+      <c r="C121" s="17" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D121" s="15" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="E121" s="18" t="inlineStr">
+        <is>
+          <t>Record the answer to the Screen Time permission prompt</t>
+        </is>
+      </c>
+      <c r="F121" s="18" t="inlineStr">
+        <is>
+          <t>The status was used to choose the next screen and then discarded, so a user who refused permission looked identical to one who never got round to it. Adds a screen_time_authorized event (approved / denied / unavailable / error). The JHU pilot reports participants as redeemed, authorized, activated; the middle step only exists if it is recorded.</t>
+        </is>
+      </c>
+      <c r="G121" s="16" t="inlineStr">
+        <is>
+          <t>1.1.7</t>
+        </is>
+      </c>
+      <c r="H121" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="40" customHeight="1">
+      <c r="A122" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B122" s="16" t="inlineStr">
+        <is>
+          <t>7aaa9ee</t>
+        </is>
+      </c>
+      <c r="C122" s="19" t="inlineStr">
+        <is>
+          <t>Bug Fix</t>
+        </is>
+      </c>
+      <c r="D122" s="15" t="inlineStr">
+        <is>
+          <t>Shield</t>
+        </is>
+      </c>
+      <c r="E122" s="18" t="inlineStr">
+        <is>
+          <t>White border around the block screen in the app switcher</t>
+        </is>
+      </c>
+      <c r="F122" s="18" t="inlineStr">
+        <is>
+          <t>The switcher snapshots the BLOCKED app's window, and the shield was composited inside it with an opaque background and no blur style, leaving that app's background at the edges. Passing a material makes iOS composite across the full snapshot; the background is drawn over it, so the shield stays solid. Verified on device.</t>
+        </is>
+      </c>
+      <c r="G122" s="16" t="inlineStr">
+        <is>
+          <t>1.1.7</t>
+        </is>
+      </c>
+      <c r="H122" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B123" s="16" t="inlineStr">
+        <is>
+          <t>20646bc</t>
+        </is>
+      </c>
+      <c r="C123" s="19" t="inlineStr">
+        <is>
+          <t>Bug Fix</t>
+        </is>
+      </c>
+      <c r="D123" s="15" t="inlineStr">
+        <is>
+          <t>AI Check</t>
+        </is>
+      </c>
+      <c r="E123" s="18" t="inlineStr">
+        <is>
+          <t>Valid photo proof rejected by a rubric that ignored the photo</t>
+        </is>
+      </c>
+      <c r="F123" s="18" t="inlineStr">
+        <is>
+          <t>Tasks classed as uncapturable ('learn', 'study') were judged 'on the written account alone', but a user may submit a photo with no text - so the judge saw '(none given)' and rejected deterministically. The rubric now branches on media. It also stops grading quality (errors in handwritten working are evidence the work was done) and stops asking the judge to establish authorship, which no photograph can settle - a deliberate product decision recorded in the file header.</t>
+        </is>
+      </c>
+      <c r="G123" s="16" t="inlineStr">
+        <is>
+          <t>1.1.7</t>
+        </is>
+      </c>
+      <c r="H123" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B124" s="16" t="inlineStr">
+        <is>
+          <t>773216b</t>
+        </is>
+      </c>
+      <c r="C124" s="19" t="inlineStr">
+        <is>
+          <t>Bug Fix</t>
+        </is>
+      </c>
+      <c r="D124" s="15" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="E124" s="18" t="inlineStr">
+        <is>
+          <t>A rate-limited token refresh permanently signed users out</t>
+        </is>
+      </c>
+      <c r="F124" s="18" t="inlineStr">
+        <is>
+          <t>auth-js retries a refresh only for 502/503/504/52x/530; anything else, including GoTrue's 429 and a 500 under load, wipes the session exactly like a revoked token. That is the 'random' logouts. A narrow shim relabels 429/500 on the refresh endpoint as 503 so auth-js backs off; a real invalid_grant still signs out. SIGNED_OUT events now record whether the app asked for them.</t>
+        </is>
+      </c>
+      <c r="G124" s="16" t="inlineStr">
+        <is>
+          <t>1.1.7</t>
+        </is>
+      </c>
+      <c r="H124" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B125" s="16" t="inlineStr">
+        <is>
+          <t>b334eb8</t>
+        </is>
+      </c>
+      <c r="C125" s="19" t="inlineStr">
+        <is>
+          <t>Bug Fix</t>
+        </is>
+      </c>
+      <c r="D125" s="15" t="inlineStr">
+        <is>
+          <t>Force update</t>
+        </is>
+      </c>
+      <c r="E125" s="18" t="inlineStr">
+        <is>
+          <t>The update gate compared marketing versions only, so it never fired within a release</t>
+        </is>
+      </c>
+      <c r="F125" s="18" t="inlineStr">
+        <is>
+          <t>Builds 118-123 are all '1.1.7', so a user on 118 was never asked to update to 123. Adds a build-number check via expo-application, scoped by min_ios_build_version so a stale minimum cannot lock out a later release line - the 2026-07-29 class of lockout. Also replaced ios_store_url, still the 'idYOUR_APP_ID' placeholder the update button would have opened.</t>
+        </is>
+      </c>
+      <c r="G125" s="16" t="inlineStr">
+        <is>
+          <t>1.1.7</t>
+        </is>
+      </c>
+      <c r="H125" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B126" s="16" t="inlineStr">
+        <is>
+          <t>ca80da3</t>
+        </is>
+      </c>
+      <c r="C126" s="19" t="inlineStr">
+        <is>
+          <t>Bug Fix</t>
+        </is>
+      </c>
+      <c r="D126" s="15" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="E126" s="18" t="inlineStr">
+        <is>
+          <t>Every screen-time sync after the first of the day failed</t>
+        </is>
+      </c>
+      <c r="F126" s="18" t="inlineStr">
+        <is>
+          <t>schema_v7 declared screen_time.updated_at inside CREATE TABLE IF NOT EXISTS on a table that already existed, so the column was never created while its trigger was, and threw on every UPDATE. The first write of a day INSERTs and succeeds, which is why the friends leaderboard showed stale screen time rather than none. Server-side; verified live 2026-09-19.</t>
+        </is>
+      </c>
+      <c r="G126" s="16" t="inlineStr">
+        <is>
+          <t>1.1.7</t>
+        </is>
+      </c>
+      <c r="H126" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B127" s="16" t="inlineStr">
+        <is>
+          <t>f61bbd1</t>
+        </is>
+      </c>
+      <c r="C127" s="20" t="inlineStr">
+        <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="D127" s="15" t="inlineStr">
+        <is>
+          <t>Dependencies</t>
+        </is>
+      </c>
+      <c r="E127" s="18" t="inlineStr">
+        <is>
+          <t>expo-constants and react-native-svg aligned with Expo SDK 54</t>
+        </is>
+      </c>
+      <c r="F127" s="18" t="inlineStr">
+        <is>
+          <t>expo-constants was pinned ^57.0.8 against SDK 54, which expects ~18.0.14; iOS tolerated it and Android did not compile. react-native-svg fixed for Fabric registration. Also 040f48c: the new store_unavailable purchase reason mapped to real copy instead of being shown to users verbatim.</t>
+        </is>
+      </c>
+      <c r="G127" s="16" t="inlineStr">
+        <is>
+          <t>1.1.7</t>
+        </is>
+      </c>
+      <c r="H127" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H114"/>
+  <autoFilter ref="A1:H127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Drift-changelog.xlsx
+++ b/Drift-changelog.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Changes'!$A$1:$H$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Changes'!$A$1:$H$133</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -586,7 +586,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every feature, fix and change shipped. 2026-07-07 – 2026-09-11.</t>
+          <t>Every feature, fix and change shipped. 2026-07-07 – 2026-09-19.</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>COUNTA(Changes!E2:E127)</f>
+        <f>COUNTA(Changes!E2:E133)</f>
         <v/>
       </c>
     </row>
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$127,A8)</f>
+        <f>COUNTIF(Changes!$C$2:$C$133,A8)</f>
         <v/>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="E8" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D8)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D8)</f>
         <v/>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="H8" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$127,G8)</f>
+        <f>COUNTIF(Changes!$G$2:$G$133,G8)</f>
         <v/>
       </c>
     </row>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$127,A9)</f>
+        <f>COUNTIF(Changes!$C$2:$C$133,A9)</f>
         <v/>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="E9" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D9)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D9)</f>
         <v/>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="H9" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$127,G9)</f>
+        <f>COUNTIF(Changes!$G$2:$G$133,G9)</f>
         <v/>
       </c>
     </row>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$127,A10)</f>
+        <f>COUNTIF(Changes!$C$2:$C$133,A10)</f>
         <v/>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="E10" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D10)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D10)</f>
         <v/>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="H10" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$127,G10)</f>
+        <f>COUNTIF(Changes!$G$2:$G$133,G10)</f>
         <v/>
       </c>
     </row>
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$127,A11)</f>
+        <f>COUNTIF(Changes!$C$2:$C$133,A11)</f>
         <v/>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="E11" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D11)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D11)</f>
         <v/>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="H11" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$127,G11)</f>
+        <f>COUNTIF(Changes!$G$2:$G$133,G11)</f>
         <v/>
       </c>
     </row>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$127,A12)</f>
+        <f>COUNTIF(Changes!$C$2:$C$133,A12)</f>
         <v/>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="E12" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D12)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D12)</f>
         <v/>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="H12" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$127,G12)</f>
+        <f>COUNTIF(Changes!$G$2:$G$133,G12)</f>
         <v/>
       </c>
     </row>
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$127,A13)</f>
+        <f>COUNTIF(Changes!$C$2:$C$133,A13)</f>
         <v/>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -811,16 +811,16 @@
         </is>
       </c>
       <c r="E13" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D13)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D13)</f>
         <v/>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Unreleased</t>
+          <t>1.1.8</t>
         </is>
       </c>
       <c r="H13" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$127,G13)</f>
+        <f>COUNTIF(Changes!$G$2:$G$133,G13)</f>
         <v/>
       </c>
     </row>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$127,A14)</f>
+        <f>COUNTIF(Changes!$C$2:$C$133,A14)</f>
         <v/>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -840,7 +840,16 @@
         </is>
       </c>
       <c r="E14" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D14)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D14)</f>
+        <v/>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Unreleased</t>
+        </is>
+      </c>
+      <c r="H14" s="7">
+        <f>COUNTIF(Changes!$G$2:$G$133,G14)</f>
         <v/>
       </c>
     </row>
@@ -851,7 +860,7 @@
         </is>
       </c>
       <c r="E15" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D15)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D15)</f>
         <v/>
       </c>
     </row>
@@ -862,7 +871,7 @@
         </is>
       </c>
       <c r="E16" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D16)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D16)</f>
         <v/>
       </c>
     </row>
@@ -873,7 +882,7 @@
         </is>
       </c>
       <c r="E17" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D17)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D17)</f>
         <v/>
       </c>
     </row>
@@ -884,370 +893,381 @@
         </is>
       </c>
       <c r="E18" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D18)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Dependencies</t>
+          <t>Cohort codes</t>
         </is>
       </c>
       <c r="E19" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D19)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Discoverability</t>
+          <t>Dependencies</t>
         </is>
       </c>
       <c r="E20" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D20)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Drift In</t>
+          <t>Discoverability</t>
         </is>
       </c>
       <c r="E21" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D21)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>Drift In</t>
         </is>
       </c>
       <c r="E22" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D22)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>Entitlement</t>
         </is>
       </c>
       <c r="E23" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D23)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D23)</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Force update</t>
+          <t>Family</t>
         </is>
       </c>
       <c r="E24" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D24)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Force update</t>
         </is>
       </c>
       <c r="E25" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D25)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Interaction</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="E26" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D26)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Lockbox</t>
+          <t>Interaction</t>
         </is>
       </c>
       <c r="E27" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D27)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D27)</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Navigation</t>
+          <t>Lockbox</t>
         </is>
       </c>
       <c r="E28" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D28)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Navigation</t>
         </is>
       </c>
       <c r="E29" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D29)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="E30" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D30)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Payments</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="E31" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D31)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Paywall</t>
+          <t>Payments</t>
         </is>
       </c>
       <c r="E32" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D32)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Paywall</t>
         </is>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D33)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D34)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D34)</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D35)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D35)</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Release</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D36)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D36)</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Release</t>
         </is>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D37)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D37)</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Scaling</t>
+          <t>Reviews</t>
         </is>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D38)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D38)</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Screen Time</t>
+          <t>Scaling</t>
         </is>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D39)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D39)</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Screen Time</t>
         </is>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D40)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D40)</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Siri</t>
+          <t>Shield</t>
         </is>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D41)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D41)</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Sleep Guard</t>
+          <t>Siri</t>
         </is>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D42)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D42)</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Social</t>
+          <t>Sleep Guard</t>
         </is>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D43)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D43)</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Tasks</t>
+          <t>Social</t>
         </is>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D44)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D44)</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Theme</t>
+          <t>Tasks</t>
         </is>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D45)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D45)</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Tour</t>
+          <t>Theme</t>
         </is>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D46)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D46)</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Tour</t>
         </is>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D47)</f>
+        <f>COUNTIF(Changes!$D$2:$D$133,D47)</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="D48" s="7" t="inlineStr">
         <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="E48" s="7">
+        <f>COUNTIF(Changes!$D$2:$D$133,D48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="D49" s="7" t="inlineStr">
+        <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="E48" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$127,D48)</f>
+      <c r="E49" s="7">
+        <f>COUNTIF(Changes!$D$2:$D$133,D49)</f>
         <v/>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="13" t="inlineStr">
-        <is>
-          <t>• 1.1.4 is the last version submitted to the App Store. Everything marked Unreleased is on main but not shipped.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="13" t="inlineStr">
         <is>
-          <t>• "Needs" says what a change requires beyond a normal JS reload: a native rebuild, an edge-function deploy, or SQL run in Supabase.</t>
+          <t>• 1.1.4 is the last version submitted to the App Store. Everything marked Unreleased is on main but not shipped.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>• Native-build items are currently blocked on Apple Developer account access, so they are not device-tested.</t>
+          <t>• "Needs" says what a change requires beyond a normal JS reload: a native rebuild, an edge-function deploy, or SQL run in Supabase.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="13" t="inlineStr">
+        <is>
+          <t>• Native-build items are currently blocked on Apple Developer account access, so they are not device-tested.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr">
         <is>
           <t>• Counts on this sheet are formulas over the Changes tab — they update if you edit, add or delete rows there.</t>
         </is>
@@ -1264,7 +1284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H127"/>
+  <dimension ref="A1:H133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6603,8 +6623,260 @@
         </is>
       </c>
     </row>
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B128" s="16" t="inlineStr">
+        <is>
+          <t>81d40da</t>
+        </is>
+      </c>
+      <c r="C128" s="17" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D128" s="15" t="inlineStr">
+        <is>
+          <t>Cohort codes</t>
+        </is>
+      </c>
+      <c r="E128" s="18" t="inlineStr">
+        <is>
+          <t>Study participants enter their participant ID when they redeem a code</t>
+        </is>
+      </c>
+      <c r="F128" s="18" t="inlineStr">
+        <is>
+          <t>The Johns Hopkins pilot reports per participant keyed on the study's own IDs, never names or emails. A code can carry participant_id_format; when set, redemption asks for the ID, checks the format, refuses one already used on that code, and stores it uppercased so 'jhu-007' and 'JHU-007' are one person. No seat is spent until the ID is accepted, and codes without a format are unchanged. cohort_participants(cohort) returns the funnel by ID only.</t>
+        </is>
+      </c>
+      <c r="G128" s="16" t="inlineStr">
+        <is>
+          <t>1.1.8</t>
+        </is>
+      </c>
+      <c r="H128" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B129" s="16" t="inlineStr">
+        <is>
+          <t>5ef1f3a</t>
+        </is>
+      </c>
+      <c r="C129" s="17" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D129" s="15" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="E129" s="18" t="inlineStr">
+        <is>
+          <t>Blocking an app is finally recorded on the server</t>
+        </is>
+      </c>
+      <c r="F129" s="18" t="inlineStr">
+        <is>
+          <t>Apple's picker keeps the selection on the device and nothing wrote the blocked_apps table, so a user who blocked apps was indistinguishable from one who never did - the 'activated' step of the pilot funnel. Now logs counts only (apps, categories, web domains), never names or tokens.</t>
+        </is>
+      </c>
+      <c r="G129" s="16" t="inlineStr">
+        <is>
+          <t>1.1.8</t>
+        </is>
+      </c>
+      <c r="H129" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="40" customHeight="1">
+      <c r="A130" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B130" s="16" t="inlineStr">
+        <is>
+          <t>affed23</t>
+        </is>
+      </c>
+      <c r="C130" s="17" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D130" s="15" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="E130" s="18" t="inlineStr">
+        <is>
+          <t>Screen views recorded per tab</t>
+        </is>
+      </c>
+      <c r="F130" s="18" t="inlineStr">
+        <is>
+          <t>trackScreen existed since analytics landed but nothing ever called it, so which features people use was invisible. Fires once per tab change.</t>
+        </is>
+      </c>
+      <c r="G130" s="16" t="inlineStr">
+        <is>
+          <t>1.1.8</t>
+        </is>
+      </c>
+      <c r="H130" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B131" s="16" t="inlineStr">
+        <is>
+          <t>c006b06</t>
+        </is>
+      </c>
+      <c r="C131" s="19" t="inlineStr">
+        <is>
+          <t>Bug Fix</t>
+        </is>
+      </c>
+      <c r="D131" s="15" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="E131" s="18" t="inlineStr">
+        <is>
+          <t>Failed event uploads were silently discarded</t>
+        </is>
+      </c>
+      <c r="F131" s="18" t="inlineStr">
+        <is>
+          <t>supabase-js returns insert errors rather than throwing them, so the bare try/catch around the flush hid every rejected batch; a day with no events read exactly like a day with no users. Dev builds now log the failure. Found while verifying the pilot funnel on device.</t>
+        </is>
+      </c>
+      <c r="G131" s="16" t="inlineStr">
+        <is>
+          <t>1.1.8</t>
+        </is>
+      </c>
+      <c r="H131" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="40" customHeight="1">
+      <c r="A132" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B132" s="16" t="inlineStr">
+        <is>
+          <t>7aaa9ee</t>
+        </is>
+      </c>
+      <c r="C132" s="19" t="inlineStr">
+        <is>
+          <t>Bug Fix</t>
+        </is>
+      </c>
+      <c r="D132" s="15" t="inlineStr">
+        <is>
+          <t>Screen Time</t>
+        </is>
+      </c>
+      <c r="E132" s="18" t="inlineStr">
+        <is>
+          <t>White border around the block screen in the app switcher</t>
+        </is>
+      </c>
+      <c r="F132" s="18" t="inlineStr">
+        <is>
+          <t>The shield drew an opaque colour with no background blur style, so the blocked app's own window showed through as a white frame in the switcher snapshot, on every blocked app regardless of theme. A material makes iOS composite the shield across the whole snapshot; the opaque ground keeps the shield itself solid in use. Verified on device.</t>
+        </is>
+      </c>
+      <c r="G132" s="16" t="inlineStr">
+        <is>
+          <t>1.1.8</t>
+        </is>
+      </c>
+      <c r="H132" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="40" customHeight="1">
+      <c r="A133" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B133" s="16" t="inlineStr">
+        <is>
+          <t>c79f41c</t>
+        </is>
+      </c>
+      <c r="C133" s="17" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D133" s="15" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="E133" s="18" t="inlineStr">
+        <is>
+          <t>The answer to Apple's Screen Time prompt is recorded</t>
+        </is>
+      </c>
+      <c r="F133" s="18" t="inlineStr">
+        <is>
+          <t>Nothing works without that permission and the answer was used then thrown away, so a signup that never blocked anything looked the same as one that refused. Wrapped at the bridge layer so every path that asks is covered.</t>
+        </is>
+      </c>
+      <c r="G133" s="16" t="inlineStr">
+        <is>
+          <t>1.1.8</t>
+        </is>
+      </c>
+      <c r="H133" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H127"/>
+  <autoFilter ref="A1:H133"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Drift-changelog.xlsx
+++ b/Drift-changelog.xlsx
@@ -816,7 +816,7 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>1.1.8</t>
+          <t>Unreleased</t>
         </is>
       </c>
       <c r="H13" s="7">
@@ -841,15 +841,6 @@
       </c>
       <c r="E14" s="7">
         <f>COUNTIF(Changes!$D$2:$D$133,D14)</f>
-        <v/>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
-        </is>
-      </c>
-      <c r="H14" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$133,G14)</f>
         <v/>
       </c>
     </row>
@@ -6656,7 +6647,7 @@
       </c>
       <c r="G128" s="16" t="inlineStr">
         <is>
-          <t>1.1.8</t>
+          <t>1.1.7</t>
         </is>
       </c>
       <c r="H128" s="16" t="inlineStr">
@@ -6698,7 +6689,7 @@
       </c>
       <c r="G129" s="16" t="inlineStr">
         <is>
-          <t>1.1.8</t>
+          <t>1.1.7</t>
         </is>
       </c>
       <c r="H129" s="16" t="inlineStr">
@@ -6740,7 +6731,7 @@
       </c>
       <c r="G130" s="16" t="inlineStr">
         <is>
-          <t>1.1.8</t>
+          <t>1.1.7</t>
         </is>
       </c>
       <c r="H130" s="16" t="inlineStr">
@@ -6782,7 +6773,7 @@
       </c>
       <c r="G131" s="16" t="inlineStr">
         <is>
-          <t>1.1.8</t>
+          <t>1.1.7</t>
         </is>
       </c>
       <c r="H131" s="16" t="inlineStr">
@@ -6824,7 +6815,7 @@
       </c>
       <c r="G132" s="16" t="inlineStr">
         <is>
-          <t>1.1.8</t>
+          <t>1.1.7</t>
         </is>
       </c>
       <c r="H132" s="16" t="inlineStr">
@@ -6866,7 +6857,7 @@
       </c>
       <c r="G133" s="16" t="inlineStr">
         <is>
-          <t>1.1.8</t>
+          <t>1.1.7</t>
         </is>
       </c>
       <c r="H133" s="16" t="inlineStr">

--- a/Drift-changelog.xlsx
+++ b/Drift-changelog.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Changes'!$A$1:$H$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Changes'!$A$1:$H$145</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -69,11 +69,6 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00B0764E"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <color rgb="00B0764E"/>
       <sz val="10"/>
     </font>
@@ -147,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -193,9 +188,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -563,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -586,7 +578,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every feature, fix and change shipped. 2026-07-07 – 2026-09-19.</t>
+          <t>Every feature, fix and change shipped. 2026-07-07 – 2026-09-29.</t>
         </is>
       </c>
     </row>
@@ -597,7 +589,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>COUNTA(Changes!E2:E133)</f>
+        <f>COUNTA(Changes!E2:E145)</f>
         <v/>
       </c>
     </row>
@@ -657,7 +649,7 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$133,A8)</f>
+        <f>COUNTIF(Changes!$C$2:$C$145,A8)</f>
         <v/>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -666,7 +658,7 @@
         </is>
       </c>
       <c r="E8" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D8)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D8)</f>
         <v/>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -675,7 +667,7 @@
         </is>
       </c>
       <c r="H8" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$133,G8)</f>
+        <f>COUNTIF(Changes!$G$2:$G$145,G8)</f>
         <v/>
       </c>
     </row>
@@ -686,7 +678,7 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$133,A9)</f>
+        <f>COUNTIF(Changes!$C$2:$C$145,A9)</f>
         <v/>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -695,7 +687,7 @@
         </is>
       </c>
       <c r="E9" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D9)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D9)</f>
         <v/>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -704,7 +696,7 @@
         </is>
       </c>
       <c r="H9" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$133,G9)</f>
+        <f>COUNTIF(Changes!$G$2:$G$145,G9)</f>
         <v/>
       </c>
     </row>
@@ -715,7 +707,7 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$133,A10)</f>
+        <f>COUNTIF(Changes!$C$2:$C$145,A10)</f>
         <v/>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -724,7 +716,7 @@
         </is>
       </c>
       <c r="E10" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D10)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D10)</f>
         <v/>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -733,7 +725,7 @@
         </is>
       </c>
       <c r="H10" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$133,G10)</f>
+        <f>COUNTIF(Changes!$G$2:$G$145,G10)</f>
         <v/>
       </c>
     </row>
@@ -744,7 +736,7 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$133,A11)</f>
+        <f>COUNTIF(Changes!$C$2:$C$145,A11)</f>
         <v/>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -753,7 +745,7 @@
         </is>
       </c>
       <c r="E11" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D11)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D11)</f>
         <v/>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -762,7 +754,7 @@
         </is>
       </c>
       <c r="H11" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$133,G11)</f>
+        <f>COUNTIF(Changes!$G$2:$G$145,G11)</f>
         <v/>
       </c>
     </row>
@@ -773,7 +765,7 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$133,A12)</f>
+        <f>COUNTIF(Changes!$C$2:$C$145,A12)</f>
         <v/>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -782,7 +774,7 @@
         </is>
       </c>
       <c r="E12" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D12)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D12)</f>
         <v/>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -791,7 +783,7 @@
         </is>
       </c>
       <c r="H12" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$133,G12)</f>
+        <f>COUNTIF(Changes!$G$2:$G$145,G12)</f>
         <v/>
       </c>
     </row>
@@ -802,7 +794,7 @@
         </is>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$133,A13)</f>
+        <f>COUNTIF(Changes!$C$2:$C$145,A13)</f>
         <v/>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -811,16 +803,16 @@
         </is>
       </c>
       <c r="E13" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D13)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D13)</f>
         <v/>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Unreleased</t>
+          <t>1.1.8</t>
         </is>
       </c>
       <c r="H13" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$133,G13)</f>
+        <f>COUNTIF(Changes!$G$2:$G$145,G13)</f>
         <v/>
       </c>
     </row>
@@ -831,7 +823,7 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$133,A14)</f>
+        <f>COUNTIF(Changes!$C$2:$C$145,A14)</f>
         <v/>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -840,7 +832,16 @@
         </is>
       </c>
       <c r="E14" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D14)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D14)</f>
+        <v/>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Unreleased</t>
+        </is>
+      </c>
+      <c r="H14" s="7">
+        <f>COUNTIF(Changes!$G$2:$G$145,G14)</f>
         <v/>
       </c>
     </row>
@@ -851,7 +852,7 @@
         </is>
       </c>
       <c r="E15" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D15)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D15)</f>
         <v/>
       </c>
     </row>
@@ -862,7 +863,7 @@
         </is>
       </c>
       <c r="E16" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D16)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D16)</f>
         <v/>
       </c>
     </row>
@@ -873,7 +874,7 @@
         </is>
       </c>
       <c r="E17" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D17)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D17)</f>
         <v/>
       </c>
     </row>
@@ -884,7 +885,7 @@
         </is>
       </c>
       <c r="E18" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D18)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D18)</f>
         <v/>
       </c>
     </row>
@@ -895,7 +896,7 @@
         </is>
       </c>
       <c r="E19" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D19)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D19)</f>
         <v/>
       </c>
     </row>
@@ -906,359 +907,392 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D20)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Discoverability</t>
+          <t>Dev</t>
         </is>
       </c>
       <c r="E21" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D21)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Drift In</t>
+          <t>Discoverability</t>
         </is>
       </c>
       <c r="E22" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D22)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>Drift In</t>
         </is>
       </c>
       <c r="E23" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D23)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D23)</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>Entitlement</t>
         </is>
       </c>
       <c r="E24" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D24)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Force update</t>
+          <t>Family</t>
         </is>
       </c>
       <c r="E25" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D25)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Force update</t>
         </is>
       </c>
       <c r="E26" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D26)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Interaction</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="E27" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D27)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D27)</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Lockbox</t>
+          <t>Interaction</t>
         </is>
       </c>
       <c r="E28" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D28)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Navigation</t>
+          <t>Lab</t>
         </is>
       </c>
       <c r="E29" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D29)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Live Activity</t>
         </is>
       </c>
       <c r="E30" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D30)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Lockbox</t>
         </is>
       </c>
       <c r="E31" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D31)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Payments</t>
+          <t>Navigation</t>
         </is>
       </c>
       <c r="E32" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D32)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Paywall</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D33)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D34)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D34)</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Payments</t>
         </is>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D35)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D35)</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Paywall</t>
         </is>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D36)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D36)</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Release</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D37)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D37)</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D38)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D38)</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Scaling</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D39)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D39)</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Screen Time</t>
+          <t>Release</t>
         </is>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D40)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D40)</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Reviews</t>
         </is>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D41)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D41)</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Siri</t>
+          <t>Scaling</t>
         </is>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D42)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D42)</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Sleep Guard</t>
+          <t>Screen Time</t>
         </is>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D43)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D43)</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Social</t>
+          <t>Shield</t>
         </is>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D44)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D44)</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Tasks</t>
+          <t>Siri</t>
         </is>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D45)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D45)</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Theme</t>
+          <t>Sleep Guard</t>
         </is>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D46)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D46)</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Tour</t>
+          <t>Social</t>
         </is>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D47)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D47)</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Tasks</t>
         </is>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D48)</f>
+        <f>COUNTIF(Changes!$D$2:$D$145,D48)</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="D49" s="7" t="inlineStr">
         <is>
+          <t>Theme</t>
+        </is>
+      </c>
+      <c r="E49" s="7">
+        <f>COUNTIF(Changes!$D$2:$D$145,D49)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Tour</t>
+        </is>
+      </c>
+      <c r="E50" s="7">
+        <f>COUNTIF(Changes!$D$2:$D$145,D50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="E51" s="7">
+        <f>COUNTIF(Changes!$D$2:$D$145,D51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="D52" s="7" t="inlineStr">
+        <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="E49" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$133,D49)</f>
+      <c r="E52" s="7">
+        <f>COUNTIF(Changes!$D$2:$D$145,D52)</f>
         <v/>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="13" t="inlineStr">
-        <is>
-          <t>• 1.1.4 is the last version submitted to the App Store. Everything marked Unreleased is on main but not shipped.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="13" t="inlineStr">
-        <is>
-          <t>• "Needs" says what a change requires beyond a normal JS reload: a native rebuild, an edge-function deploy, or SQL run in Supabase.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="13" t="inlineStr">
-        <is>
-          <t>• Native-build items are currently blocked on Apple Developer account access, so they are not device-tested.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>• 1.1.8 is the last version submitted to the App Store. Everything marked Unreleased is on main but not shipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="13" t="inlineStr">
+        <is>
+          <t>• "Needs" says what a change requires beyond a normal JS reload: a native rebuild, an edge-function deploy, or SQL run in Supabase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>• Native-build items are currently blocked on Apple Developer account access, so they are not device-tested.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>• Counts on this sheet are formulas over the Changes tab — they update if you edit, add or delete rows there.</t>
         </is>
@@ -1275,7 +1309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H133"/>
+  <dimension ref="A1:H145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3041,9 +3075,9 @@
           <t>All four tabs stay mounted, so every timer tick re-rendered the whole Grove tree and starved the JS thread. Memoized the screens and gave them stable props.</t>
         </is>
       </c>
-      <c r="G42" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G42" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H42" s="16" t="inlineStr">
@@ -3083,9 +3117,9 @@
           <t>Activated the dormant MoveNet pose pipeline (a stub file had been shadowing it on every build). Camera counts reps and auto-verifies; photo check remains as fallback.</t>
         </is>
       </c>
-      <c r="G43" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G43" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H43" s="22" t="inlineStr">
@@ -3125,9 +3159,9 @@
           <t>Organic-editorial restyle with LIVE badges on pose-tracked exercises and a plain-language stakes card.</t>
         </is>
       </c>
-      <c r="G44" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G44" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H44" s="16" t="inlineStr">
@@ -3167,9 +3201,9 @@
           <t>Thumb-reachable bottom dock for the task name.</t>
         </is>
       </c>
-      <c r="G45" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G45" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H45" s="16" t="inlineStr">
@@ -3205,9 +3239,9 @@
         </is>
       </c>
       <c r="F46" s="18" t="inlineStr"/>
-      <c r="G46" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G46" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H46" s="16" t="inlineStr">
@@ -3243,9 +3277,9 @@
         </is>
       </c>
       <c r="F47" s="18" t="inlineStr"/>
-      <c r="G47" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G47" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H47" s="16" t="inlineStr">
@@ -3285,9 +3319,9 @@
           <t>Manual trigger with platform + profile inputs. Blocked on Apple Developer account credentials.</t>
         </is>
       </c>
-      <c r="G48" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G48" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H48" s="16" t="inlineStr">
@@ -3327,9 +3361,9 @@
           <t>Version lookup used app.json's bundle id (com.drift.app) but the signed app is com.sanghani.drift, so iTunes returned nothing. Corrected both.</t>
         </is>
       </c>
-      <c r="G49" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G49" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H49" s="16" t="inlineStr">
@@ -3369,9 +3403,9 @@
           <t>Two code paths fired it, and both re-fired on every app reopen. Now latched with persisted flags: one notification per depletion, re-armed when the balance goes positive.</t>
         </is>
       </c>
-      <c r="G50" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G50" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H50" s="16" t="inlineStr">
@@ -3411,9 +3445,9 @@
           <t>Save your own places (gym, office); arriving fires a notification that opens a prefilled, editable confirm sheet. Coordinates never leave the device — no Places API.</t>
         </is>
       </c>
-      <c r="G51" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G51" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H51" s="22" t="inlineStr">
@@ -3453,9 +3487,9 @@
           <t>Read-only import of today's events as tasks, deduped by event id so re-syncing never duplicates.</t>
         </is>
       </c>
-      <c r="G52" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G52" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H52" s="22" t="inlineStr">
@@ -3495,9 +3529,9 @@
           <t>Category picker removed entirely. Classified server-side in the same round trip that values the task, against a fixed whitelist validated on both ends.</t>
         </is>
       </c>
-      <c r="G53" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G53" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H53" s="22" t="inlineStr">
@@ -3537,9 +3571,9 @@
           <t>Google-backed calendars detected, badged, sorted first and preselected; device calendars remain switchable.</t>
         </is>
       </c>
-      <c r="G54" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G54" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H54" s="22" t="inlineStr">
@@ -3579,9 +3613,9 @@
           <t>Was a permanent block of text; now one icon that reveals it on tap.</t>
         </is>
       </c>
-      <c r="G55" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G55" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H55" s="16" t="inlineStr">
@@ -3621,9 +3655,9 @@
           <t>Optional opt-in step at the end of onboarding, a one-line dismissible nudge on Today, and a single line in Add Task. All self-removing once acted on.</t>
         </is>
       </c>
-      <c r="G56" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G56" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H56" s="16" t="inlineStr">
@@ -3663,9 +3697,9 @@
           <t>Five always-visible pills replaced by one row that expands into a list.</t>
         </is>
       </c>
-      <c r="G57" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G57" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H57" s="16" t="inlineStr">
@@ -3705,9 +3739,9 @@
           <t>Fills the space the category picker left; 15m/30m/1h/2h chips snap to the slider's step.</t>
         </is>
       </c>
-      <c r="G58" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G58" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H58" s="16" t="inlineStr">
@@ -3747,9 +3781,9 @@
           <t>Holds blocked apps/hours, automatic tasks, recurring tasks and tour replay, moved out of Profile. Stats merged into The Grove to make room.</t>
         </is>
       </c>
-      <c r="G59" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G59" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H59" s="16" t="inlineStr">
@@ -3789,9 +3823,9 @@
           <t>Explicit connect prompt with an iPhone-calendar fallback; auto-import became a setting (default on).</t>
         </is>
       </c>
-      <c r="G60" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G60" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H60" s="22" t="inlineStr">
@@ -3831,9 +3865,9 @@
           <t>Replaced the five hardcoded presets; alias matching so 'uni' finds Campus and 'grocery' finds Supermarket.</t>
         </is>
       </c>
-      <c r="G61" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G61" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H61" s="16" t="inlineStr">
@@ -3873,9 +3907,9 @@
           <t>Gate only applies where blocking is actually possible, so builds without FamilyControls can't be trapped in onboarding.</t>
         </is>
       </c>
-      <c r="G62" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G62" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H62" s="16" t="inlineStr">
@@ -3915,9 +3949,9 @@
           <t>Plus DEV jump buttons gated on __DEV__.</t>
         </is>
       </c>
-      <c r="G63" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G63" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H63" s="16" t="inlineStr">
@@ -3957,9 +3991,9 @@
           <t>iOS Screen Time re-applies shields on ~15-minute granularity, so 1/3/7/15 all behaved like 15.</t>
         </is>
       </c>
-      <c r="G64" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G64" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H64" s="16" t="inlineStr">
@@ -3999,9 +4033,9 @@
           <t>Sign-in set screen='app' while XP was still 0, so hydrating real XP read as a level gain.</t>
         </is>
       </c>
-      <c r="G65" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G65" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H65" s="16" t="inlineStr">
@@ -4041,9 +4075,9 @@
           <t>XP stays uncapped.</t>
         </is>
       </c>
-      <c r="G66" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G66" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H66" s="16" t="inlineStr">
@@ -4083,9 +4117,9 @@
           <t>Ref resolved to the parent row under view flattening; Today now scrolls to top before the tour measures.</t>
         </is>
       </c>
-      <c r="G67" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G67" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H67" s="16" t="inlineStr">
@@ -4125,9 +4159,9 @@
           <t>A silent 429 reached the client as 'couldn't connect', indistinguishable from being offline. Every rejection path now logs a reason.</t>
         </is>
       </c>
-      <c r="G68" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G68" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H68" s="22" t="inlineStr">
@@ -4167,9 +4201,9 @@
           <t>Also skips AI verification for tasks with no capturable proof, failing open.</t>
         </is>
       </c>
-      <c r="G69" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G69" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H69" s="22" t="inlineStr">
@@ -4209,9 +4243,9 @@
           <t>#1F3A2A raised to #3A6B4F — 5.7:1 on cream.</t>
         </is>
       </c>
-      <c r="G70" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G70" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H70" s="16" t="inlineStr">
@@ -4251,9 +4285,9 @@
           <t>Via optional expo-haptics.</t>
         </is>
       </c>
-      <c r="G71" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G71" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H71" s="16" t="inlineStr">
@@ -4293,9 +4327,9 @@
           <t>Listed what to verify in risk order; nothing in that batch was device-verified.</t>
         </is>
       </c>
-      <c r="G72" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G72" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H72" s="16" t="inlineStr">
@@ -4335,9 +4369,9 @@
           <t>Raised ink.border 0.15→0.28 and ink.hairline 0.09→0.18.</t>
         </is>
       </c>
-      <c r="G73" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G73" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H73" s="16" t="inlineStr">
@@ -4377,9 +4411,9 @@
           <t>app.json declared version 1.0.0 while the native build was 1.1.4 (MARKETING_VERSION / CFBundleShortVersionString). The force-update gate reads Constants.expoConfig.version, which comes from app.json rather than the native build settings, so every install compared 1.0.0 against the live App Store version and blocked behind ForceUpdateModal — which has no dismiss. Set app.json and package.json to 1.1.4. The two values are independent and nothing keeps them in sync.</t>
         </is>
       </c>
-      <c r="G74" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G74" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H74" s="22" t="inlineStr">
@@ -4419,9 +4453,9 @@
           <t>appleSignIn.js was fully implemented but its import in OnboardingScreen.jsx was commented out and the button never rendered, so only Google was offered. We replied to Apple asserting we had it, which is why it bounced twice.</t>
         </is>
       </c>
-      <c r="G75" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G75" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H75" s="22" t="inlineStr">
@@ -4461,9 +4495,9 @@
           <t>ReviewPromptScreen was triggered by the tutorial's onDone, before the user had done anything. Moved into completeTask(): fires once ever, after the 3rd completed task, gated on a persisted AsyncStorage flag.</t>
         </is>
       </c>
-      <c r="G76" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G76" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H76" s="22" t="inlineStr">
@@ -4503,9 +4537,9 @@
           <t>Recovery path for the lockout above — the gate returns before every other screen, so there is nothing else to tap. Seven taps on the sprout (or visible under __DEV__); deliberately not a plain button, which would defeat forcing a real security update. The grant is stored as the version it was issued for, so it self-clears on the next update instead of disabling the gate forever.</t>
         </is>
       </c>
-      <c r="G77" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G77" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H77" s="22" t="inlineStr">
@@ -4545,9 +4579,9 @@
           <t>Guideline 3.1.2(c) auto-rejected the submission twice for its absence. The app still ships dormant auto-renewable-subscription code, so Apple's automated check applies subscription rules regardless of the paywall being disabled, and in-app links do not satisfy the scanner — it reads the store listing.</t>
         </is>
       </c>
-      <c r="G78" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G78" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H78" s="16" t="inlineStr">
@@ -4587,9 +4621,9 @@
           <t>The function was live and ACTIVE on Supabase with no source in the repo — the only copy was on Supabase's servers, so nobody could review or redeploy it. Downloaded via `supabase functions download`.</t>
         </is>
       </c>
-      <c r="G79" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G79" s="16" t="inlineStr">
+        <is>
+          <t>1.1.6</t>
         </is>
       </c>
       <c r="H79" s="16" t="inlineStr">
@@ -5217,9 +5251,9 @@
           <t>verify-task was redeployed on 2026-08-20 making taskId mandatory with a deliberate no-fallback policy, but the client change that sends taskId never shipped - the build in users' hands is 65, which still sends only taskTitle/durationMins. Every submission returned task_id_required (400) for four days. An old client naming a task by TITLE now gets the row looked up instead: the lookup runs through the caller's own RLS-scoped client and returns a real row, so created_at, minutes and the attempt count still come from the database and the time gate still holds - the title only chooses WHICH of the caller's own rows is being checked. user_id is pinned explicitly because the 'tasks: parent select' policy would otherwise let a parent's submission resolve onto a child's identically-named task. Temporary: delete once the taskId-sending build is the minimum supported version.</t>
         </is>
       </c>
-      <c r="G94" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G94" s="16" t="inlineStr">
+        <is>
+          <t>1.1.7</t>
         </is>
       </c>
       <c r="H94" s="22" t="inlineStr">
@@ -5259,9 +5293,9 @@
           <t>The client looked for the error body at res.error.context.response. In functions-js error.context IS the Response; there is no .response wrapper, so body stayed null and every status under 500 fell through to a generic 'the AI service rejected the request (error N)' alert. That is why a four-day outage surfaced as an unexplained 400 instead of the server's own 'Update Drift'. The 402 paywall, 425 too-early, follow-up-question and ai_error branches all read body, so they were silently dead too.</t>
         </is>
       </c>
-      <c r="G95" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G95" s="16" t="inlineStr">
+        <is>
+          <t>1.1.7</t>
         </is>
       </c>
       <c r="H95" s="16" t="inlineStr">
@@ -5301,9 +5335,9 @@
           <t>The deployed function was pinned at the 2026-08-20 16:18 build, predating retroactive-task support and the ask-a-clarifying-question-before-rejecting flow. Caught by diffing the downloaded artifact against the repo - worth doing routinely, since nothing in the deploy path reports drift.</t>
         </is>
       </c>
-      <c r="G96" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G96" s="16" t="inlineStr">
+        <is>
+          <t>1.1.7</t>
         </is>
       </c>
       <c r="H96" s="22" t="inlineStr">
@@ -5343,9 +5377,9 @@
           <t>The gate (no proof until half the task duration has elapsed) is server-only behaviour that has never shipped in a client. Build 65 has no countdown, no 'unlocks in 30 min' copy and no branch for 425 - it reads only 402 and 429 by status - so a 60-minute task had a 30-minute window where AI Check just errored with no visible reason. The gate now applies only to clients that send a taskId, which are exactly the clients that can render the countdown and the reason. Same class of mistake as the 400 above: a rule enforced server-side that the client in users' hands cannot express.</t>
         </is>
       </c>
-      <c r="G97" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G97" s="16" t="inlineStr">
+        <is>
+          <t>1.1.7</t>
         </is>
       </c>
       <c r="H97" s="22" t="inlineStr">
@@ -5385,9 +5419,9 @@
           <t>The compat path resolves a task by title, and same-title duplicates turn out to be the norm rather than an exception - production carries up to 23 unfinished rows under one title, spanning 19 days, because people re-add 'Make Bed' every morning. Newest-first lands on today's instance correctly, but the client marks ITS row done locally rather than whichever row the server stamped, so two same-titled tasks added on one day could diverge and the next honest submission would come back 'already verified'. Selection now prefers a row that is neither done nor already stamped. Replay protection is unaffected: when the replayed row is the only candidate it is still the one picked. A failed lookup now returns 503 rather than 404, which had been telling users to refresh a list that was fine.</t>
         </is>
       </c>
-      <c r="G98" s="25" t="inlineStr">
-        <is>
-          <t>Unreleased</t>
+      <c r="G98" s="16" t="inlineStr">
+        <is>
+          <t>1.1.7</t>
         </is>
       </c>
       <c r="H98" s="22" t="inlineStr">
@@ -6866,8 +6900,512 @@
         </is>
       </c>
     </row>
+    <row r="134" ht="40" customHeight="1">
+      <c r="A134" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B134" s="16" t="inlineStr">
+        <is>
+          <t>e1f32a0</t>
+        </is>
+      </c>
+      <c r="C134" s="19" t="inlineStr">
+        <is>
+          <t>Bug Fix</t>
+        </is>
+      </c>
+      <c r="D134" s="15" t="inlineStr">
+        <is>
+          <t>Screen Time</t>
+        </is>
+      </c>
+      <c r="E134" s="18" t="inlineStr">
+        <is>
+          <t>Screen Time permission popup nagged on every open</t>
+        </is>
+      </c>
+      <c r="F134" s="18" t="inlineStr">
+        <is>
+          <t>AuthorizationCenter briefly reports notDetermined on a cold launch, and the app trusted that single read, so users who had already granted access were asked again every time. Now re-reads before believing it and caps the prompt at once a day.</t>
+        </is>
+      </c>
+      <c r="G134" s="16" t="inlineStr">
+        <is>
+          <t>1.1.8</t>
+        </is>
+      </c>
+      <c r="H134" s="22" t="inlineStr">
+        <is>
+          <t>Native build</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="40" customHeight="1">
+      <c r="A135" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B135" s="16" t="inlineStr">
+        <is>
+          <t>e1f32a0</t>
+        </is>
+      </c>
+      <c r="C135" s="23" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D135" s="15" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="E135" s="18" t="inlineStr">
+        <is>
+          <t>Lockbox setup, action plan and sleep guard moved to sliders</t>
+        </is>
+      </c>
+      <c r="F135" s="18" t="inlineStr">
+        <is>
+          <t>Lockbox setup uses the Drift In layout with a 15m-5h PlantSlider and the reward capped at 60m. Action plan and sleep guard swap free-entry fields for sliders and lose most of their copy. The sleep-in-another-room card shows once after onboarding, then lives in The Lab.</t>
+        </is>
+      </c>
+      <c r="G135" s="16" t="inlineStr">
+        <is>
+          <t>1.1.8</t>
+        </is>
+      </c>
+      <c r="H135" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="40" customHeight="1">
+      <c r="A136" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B136" s="16" t="inlineStr">
+        <is>
+          <t>0a2ebee</t>
+        </is>
+      </c>
+      <c r="C136" s="17" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D136" s="15" t="inlineStr">
+        <is>
+          <t>Lockbox</t>
+        </is>
+      </c>
+      <c r="E136" s="18" t="inlineStr">
+        <is>
+          <t>Lockbox rebuilt: camera-style placement, real in-box check, screen-off sessions</t>
+        </is>
+      </c>
+      <c r="F136" s="18" t="inlineStr">
+        <is>
+          <t>Placement is full screen like the Camera app and the box is pinned to an ARAnchor with a saved world map, so it stays put when the camera pauses and resumes. 'In the box' now means the AR camera tracked the phone into the box's footprint; before, any flat and still phone counted, including one a metre away. The screen may turn off mid-session: CMSensorRecorder logs motion while suspended and the stretch is judged on return. Picking the phone up brings the camera back with a 10s grace period. Commits 2031aeb, 3abe58d, 868cfb5, 302a1fb.</t>
+        </is>
+      </c>
+      <c r="G136" s="16" t="inlineStr">
+        <is>
+          <t>1.1.8</t>
+        </is>
+      </c>
+      <c r="H136" s="22" t="inlineStr">
+        <is>
+          <t>Native build</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="40" customHeight="1">
+      <c r="A137" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B137" s="16" t="inlineStr">
+        <is>
+          <t>3abe58d</t>
+        </is>
+      </c>
+      <c r="C137" s="19" t="inlineStr">
+        <is>
+          <t>Bug Fix</t>
+        </is>
+      </c>
+      <c r="D137" s="15" t="inlineStr">
+        <is>
+          <t>Lockbox</t>
+        </is>
+      </c>
+      <c r="E137" s="18" t="inlineStr">
+        <is>
+          <t>Lockbox could leave an invisible layer that swallowed every tap</t>
+        </is>
+      </c>
+      <c r="F137" s="18" t="inlineStr">
+        <is>
+          <t>Placement ran in a presented Modal that could stay on screen after its view unmounted, covering the app. Lockbox now asks the shell to hide its header and tab bar instead of presenting a Modal.</t>
+        </is>
+      </c>
+      <c r="G137" s="16" t="inlineStr">
+        <is>
+          <t>1.1.8</t>
+        </is>
+      </c>
+      <c r="H137" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="40" customHeight="1">
+      <c r="A138" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B138" s="16" t="inlineStr">
+        <is>
+          <t>0a2ebee</t>
+        </is>
+      </c>
+      <c r="C138" s="17" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D138" s="15" t="inlineStr">
+        <is>
+          <t>Live Activity</t>
+        </is>
+      </c>
+      <c r="E138" s="18" t="inlineStr">
+        <is>
+          <t>Lock screen countdown keeps running while the app is suspended</t>
+        </is>
+      </c>
+      <c r="F138" s="18" t="inlineStr">
+        <is>
+          <t>The Live Activity now carries an end date, so iOS counts down on its own. Lockbox sessions start one with their real duration and a Lockbox heading, and the session end is also scheduled as a notification.</t>
+        </is>
+      </c>
+      <c r="G138" s="16" t="inlineStr">
+        <is>
+          <t>1.1.8</t>
+        </is>
+      </c>
+      <c r="H138" s="22" t="inlineStr">
+        <is>
+          <t>Native build</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="40" customHeight="1">
+      <c r="A139" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B139" s="16" t="inlineStr">
+        <is>
+          <t>4073d1c</t>
+        </is>
+      </c>
+      <c r="C139" s="17" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D139" s="15" t="inlineStr">
+        <is>
+          <t>Paywall</t>
+        </is>
+      </c>
+      <c r="E139" s="18" t="inlineStr">
+        <is>
+          <t>Separate Pro and Family paywalls, cut to the essentials</t>
+        </is>
+      </c>
+      <c r="F139" s="18" t="inlineStr">
+        <is>
+          <t>Personal accounts see only Drift Pro; parent accounts see only Drift Family with a 1-5 kids selector. The offer is a headline, three benefits, the plan, one button and one row of Restore / Terms / Privacy / code / Sign out. Required App Store disclosures unchanged. Also b3ec9ca.</t>
+        </is>
+      </c>
+      <c r="G139" s="16" t="inlineStr">
+        <is>
+          <t>1.1.8</t>
+        </is>
+      </c>
+      <c r="H139" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="40" customHeight="1">
+      <c r="A140" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B140" s="16" t="inlineStr">
+        <is>
+          <t>3d70e79</t>
+        </is>
+      </c>
+      <c r="C140" s="19" t="inlineStr">
+        <is>
+          <t>Bug Fix</t>
+        </is>
+      </c>
+      <c r="D140" s="15" t="inlineStr">
+        <is>
+          <t>Paywall</t>
+        </is>
+      </c>
+      <c r="E140" s="18" t="inlineStr">
+        <is>
+          <t>Restore with no purchases showed 'Nothing to restore' even when the App Store was unreachable</t>
+        </is>
+      </c>
+      <c r="F140" s="18" t="inlineStr">
+        <is>
+          <t>A StoreKit error was reported the same as an empty restore. It now says the App Store couldn't be reached. Terms and Privacy links point at driftproductivity.com like the rest of the app, and RevenueCat's error logs no longer red-screen dev builds.</t>
+        </is>
+      </c>
+      <c r="G140" s="16" t="inlineStr">
+        <is>
+          <t>1.1.8</t>
+        </is>
+      </c>
+      <c r="H140" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="40" customHeight="1">
+      <c r="A141" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B141" s="16" t="inlineStr">
+        <is>
+          <t>454e3db</t>
+        </is>
+      </c>
+      <c r="C141" s="19" t="inlineStr">
+        <is>
+          <t>Bug Fix</t>
+        </is>
+      </c>
+      <c r="D141" s="15" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="E141" s="18" t="inlineStr">
+        <is>
+          <t>Sign-up email had no code, so the code screen could never be completed</t>
+        </is>
+      </c>
+      <c r="F141" s="18" t="inlineStr">
+        <is>
+          <t>Supabase was generating an 8-digit OTP (mailer_otp_length = 8) but the Confirm signup template only contained the confirmation link, so the code the app asks for never reached the user. The live template now shows the code and puts it in the subject. Recorded in supabase/templates/confirmation.html.</t>
+        </is>
+      </c>
+      <c r="G141" s="16" t="inlineStr">
+        <is>
+          <t>1.1.8</t>
+        </is>
+      </c>
+      <c r="H141" s="22" t="inlineStr">
+        <is>
+          <t>Dashboard template</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="40" customHeight="1">
+      <c r="A142" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B142" s="16" t="inlineStr">
+        <is>
+          <t>59904fe</t>
+        </is>
+      </c>
+      <c r="C142" s="17" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D142" s="15" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="E142" s="18" t="inlineStr">
+        <is>
+          <t>Kids manage app access behind the parent PIN</t>
+        </is>
+      </c>
+      <c r="F142" s="18" t="inlineStr">
+        <is>
+          <t>'Manage app access' opens a PIN pad; the right parent PIN opens Apple's picker directly. Removes the ask-to-allow request flow and the parent's App requests queue.</t>
+        </is>
+      </c>
+      <c r="G142" s="16" t="inlineStr">
+        <is>
+          <t>1.1.8</t>
+        </is>
+      </c>
+      <c r="H142" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="40" customHeight="1">
+      <c r="A143" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B143" s="16" t="inlineStr">
+        <is>
+          <t>b3ec9ca</t>
+        </is>
+      </c>
+      <c r="C143" s="17" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D143" s="15" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="E143" s="18" t="inlineStr">
+        <is>
+          <t>Weekly family stats on the parent home</t>
+        </is>
+      </c>
+      <c r="F143" s="18" t="inlineStr">
+        <is>
+          <t>Once a kid joins, the family code and PIN move into the profile sheet and the home shows This week: tasks done, minutes earned, best streak, and a 7-day bar chart. Each kid row shows minutes left, tasks this week and streak.</t>
+        </is>
+      </c>
+      <c r="G143" s="16" t="inlineStr">
+        <is>
+          <t>1.1.8</t>
+        </is>
+      </c>
+      <c r="H143" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="40" customHeight="1">
+      <c r="A144" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B144" s="16" t="inlineStr">
+        <is>
+          <t>b3ec9ca</t>
+        </is>
+      </c>
+      <c r="C144" s="19" t="inlineStr">
+        <is>
+          <t>Bug Fix</t>
+        </is>
+      </c>
+      <c r="D144" s="15" t="inlineStr">
+        <is>
+          <t>Payments</t>
+        </is>
+      </c>
+      <c r="E144" s="18" t="inlineStr">
+        <is>
+          <t>Family seats were never enforced</t>
+        </is>
+      </c>
+      <c r="F144" s="18" t="inlineStr">
+        <is>
+          <t>Any family plan covered unlimited children. schema_v19 adds family_seats() as the one definition used by is_pro() and join-family; the RevenueCat webhook writes the purchased seat count, grants and codes can carry seats, and join-family refuses when no seat is free. Backfill keeps grant-covered kids. Applied and deployed 2026-09-29, verified live 2026-10-01.</t>
+        </is>
+      </c>
+      <c r="G144" s="16" t="inlineStr">
+        <is>
+          <t>1.1.8</t>
+        </is>
+      </c>
+      <c r="H144" s="22" t="inlineStr">
+        <is>
+          <t>SQL migration, Edge deploy</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="40" customHeight="1">
+      <c r="A145" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B145" s="16" t="inlineStr">
+        <is>
+          <t>bb56a59</t>
+        </is>
+      </c>
+      <c r="C145" s="21" t="inlineStr">
+        <is>
+          <t>Chore</t>
+        </is>
+      </c>
+      <c r="D145" s="15" t="inlineStr">
+        <is>
+          <t>Dev</t>
+        </is>
+      </c>
+      <c r="E145" s="18" t="inlineStr">
+        <is>
+          <t>Signing out of the team test address deletes that account</t>
+        </is>
+      </c>
+      <c r="F145" s="18" t="inlineStr">
+        <is>
+          <t>So driftappcontact@gmail.com (and +tag variants) can be reused for fresh sign-up tests. Uses the existing delete-account function, which only acts on the caller. Scoped to that address only; also in release builds. 4bf228a stops the resulting stale-session error from red-screening dev builds.</t>
+        </is>
+      </c>
+      <c r="G145" s="16" t="inlineStr">
+        <is>
+          <t>1.1.8</t>
+        </is>
+      </c>
+      <c r="H145" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H133"/>
+  <autoFilter ref="A1:H145"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Drift-changelog.xlsx
+++ b/Drift-changelog.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Changes'!$A$1:$H$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Changes'!$A$1:$H$150</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -578,7 +578,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every feature, fix and change shipped. 2026-07-07 – 2026-09-29.</t>
+          <t>Every feature, fix and change shipped. 2026-07-07 – 2026-10-01.</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>COUNTA(Changes!E2:E145)</f>
+        <f>COUNTA(Changes!E2:E150)</f>
         <v/>
       </c>
     </row>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$145,A8)</f>
+        <f>COUNTIF(Changes!$C$2:$C$150,A8)</f>
         <v/>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="E8" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D8)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D8)</f>
         <v/>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="H8" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$145,G8)</f>
+        <f>COUNTIF(Changes!$G$2:$G$150,G8)</f>
         <v/>
       </c>
     </row>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$145,A9)</f>
+        <f>COUNTIF(Changes!$C$2:$C$150,A9)</f>
         <v/>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="E9" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D9)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D9)</f>
         <v/>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="H9" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$145,G9)</f>
+        <f>COUNTIF(Changes!$G$2:$G$150,G9)</f>
         <v/>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$145,A10)</f>
+        <f>COUNTIF(Changes!$C$2:$C$150,A10)</f>
         <v/>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="E10" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D10)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D10)</f>
         <v/>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="H10" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$145,G10)</f>
+        <f>COUNTIF(Changes!$G$2:$G$150,G10)</f>
         <v/>
       </c>
     </row>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$145,A11)</f>
+        <f>COUNTIF(Changes!$C$2:$C$150,A11)</f>
         <v/>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="E11" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D11)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D11)</f>
         <v/>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="H11" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$145,G11)</f>
+        <f>COUNTIF(Changes!$G$2:$G$150,G11)</f>
         <v/>
       </c>
     </row>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$145,A12)</f>
+        <f>COUNTIF(Changes!$C$2:$C$150,A12)</f>
         <v/>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="E12" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D12)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D12)</f>
         <v/>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="H12" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$145,G12)</f>
+        <f>COUNTIF(Changes!$G$2:$G$150,G12)</f>
         <v/>
       </c>
     </row>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$145,A13)</f>
+        <f>COUNTIF(Changes!$C$2:$C$150,A13)</f>
         <v/>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="E13" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D13)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D13)</f>
         <v/>
       </c>
       <c r="G13" s="7" t="inlineStr">
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="H13" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$145,G13)</f>
+        <f>COUNTIF(Changes!$G$2:$G$150,G13)</f>
         <v/>
       </c>
     </row>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$145,A14)</f>
+        <f>COUNTIF(Changes!$C$2:$C$150,A14)</f>
         <v/>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="E14" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D14)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D14)</f>
         <v/>
       </c>
       <c r="G14" s="7" t="inlineStr">
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="H14" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$145,G14)</f>
+        <f>COUNTIF(Changes!$G$2:$G$150,G14)</f>
         <v/>
       </c>
     </row>
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="E15" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D15)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D15)</f>
         <v/>
       </c>
     </row>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="E16" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D16)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D16)</f>
         <v/>
       </c>
     </row>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="E17" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D17)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D17)</f>
         <v/>
       </c>
     </row>
@@ -885,414 +885,425 @@
         </is>
       </c>
       <c r="E18" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D18)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Cohort codes</t>
+          <t>Codes</t>
         </is>
       </c>
       <c r="E19" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D19)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Dependencies</t>
+          <t>Cohort codes</t>
         </is>
       </c>
       <c r="E20" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D20)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Dev</t>
+          <t>Dependencies</t>
         </is>
       </c>
       <c r="E21" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D21)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Discoverability</t>
+          <t>Dev</t>
         </is>
       </c>
       <c r="E22" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D22)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Drift In</t>
+          <t>Discoverability</t>
         </is>
       </c>
       <c r="E23" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D23)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D23)</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>Drift In</t>
         </is>
       </c>
       <c r="E24" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D24)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>Entitlement</t>
         </is>
       </c>
       <c r="E25" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D25)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Force update</t>
+          <t>Family</t>
         </is>
       </c>
       <c r="E26" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D26)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Force update</t>
         </is>
       </c>
       <c r="E27" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D27)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D27)</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Interaction</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="E28" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D28)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Lab</t>
+          <t>Interaction</t>
         </is>
       </c>
       <c r="E29" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D29)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Live Activity</t>
+          <t>Lab</t>
         </is>
       </c>
       <c r="E30" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D30)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Lockbox</t>
+          <t>Live Activity</t>
         </is>
       </c>
       <c r="E31" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D31)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Navigation</t>
+          <t>Lockbox</t>
         </is>
       </c>
       <c r="E32" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D32)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Navigation</t>
         </is>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D33)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D34)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D34)</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Payments</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D35)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D35)</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Paywall</t>
+          <t>Payments</t>
         </is>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D36)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D36)</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Paywall</t>
         </is>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D37)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D37)</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D38)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D38)</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D39)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D39)</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Release</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D40)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D40)</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Release</t>
         </is>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D41)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D41)</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Scaling</t>
+          <t>Reviews</t>
         </is>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D42)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D42)</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Screen Time</t>
+          <t>Scaling</t>
         </is>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D43)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D43)</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Screen Time</t>
         </is>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D44)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D44)</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Siri</t>
+          <t>Shield</t>
         </is>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D45)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D45)</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Sleep Guard</t>
+          <t>Siri</t>
         </is>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D46)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D46)</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Social</t>
+          <t>Sleep Guard</t>
         </is>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D47)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D47)</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Tasks</t>
+          <t>Social</t>
         </is>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D48)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D48)</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Theme</t>
+          <t>Tasks</t>
         </is>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D49)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D49)</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Tour</t>
+          <t>Theme</t>
         </is>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D50)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D50)</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Tour</t>
         </is>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D51)</f>
+        <f>COUNTIF(Changes!$D$2:$D$150,D51)</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="D52" s="7" t="inlineStr">
         <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="E52" s="7">
+        <f>COUNTIF(Changes!$D$2:$D$150,D52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="D53" s="7" t="inlineStr">
+        <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="E52" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$145,D52)</f>
+      <c r="E53" s="7">
+        <f>COUNTIF(Changes!$D$2:$D$150,D53)</f>
         <v/>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="13" t="inlineStr">
-        <is>
-          <t>• 1.1.8 is the last version submitted to the App Store. Everything marked Unreleased is on main but not shipped.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="13" t="inlineStr">
         <is>
-          <t>• "Needs" says what a change requires beyond a normal JS reload: a native rebuild, an edge-function deploy, or SQL run in Supabase.</t>
+          <t>• 1.1.8 is the last version submitted to the App Store. Everything marked Unreleased is on main but not shipped.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>• Native-build items are currently blocked on Apple Developer account access, so they are not device-tested.</t>
+          <t>• "Needs" says what a change requires beyond a normal JS reload: a native rebuild, an edge-function deploy, or SQL run in Supabase.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>• Native-build items are currently blocked on Apple Developer account access, so they are not device-tested.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
         <is>
           <t>• Counts on this sheet are formulas over the Changes tab — they update if you edit, add or delete rows there.</t>
         </is>
@@ -1309,7 +1320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H145"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7404,8 +7415,218 @@
         </is>
       </c>
     </row>
+    <row r="146" ht="40" customHeight="1">
+      <c r="A146" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B146" s="16" t="inlineStr">
+        <is>
+          <t>56843dd</t>
+        </is>
+      </c>
+      <c r="C146" s="19" t="inlineStr">
+        <is>
+          <t>Bug Fix</t>
+        </is>
+      </c>
+      <c r="D146" s="15" t="inlineStr">
+        <is>
+          <t>Lockbox</t>
+        </is>
+      </c>
+      <c r="E146" s="18" t="inlineStr">
+        <is>
+          <t>A finished Lockbox session could pay out twice</t>
+        </is>
+      </c>
+      <c r="F146" s="18" t="inlineStr">
+        <is>
+          <t>finishSession read the session, appended history, then cleared it, with nothing stopping a second caller in between. The countdown, the grace ticker and the End button can all settle at once, so overlapping calls each saw the session and each wrote a paid record. It is now serialized; the second caller gets null.</t>
+        </is>
+      </c>
+      <c r="G146" s="16" t="inlineStr">
+        <is>
+          <t>1.1.8</t>
+        </is>
+      </c>
+      <c r="H146" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="40" customHeight="1">
+      <c r="A147" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B147" s="16" t="inlineStr">
+        <is>
+          <t>56843dd</t>
+        </is>
+      </c>
+      <c r="C147" s="19" t="inlineStr">
+        <is>
+          <t>Bug Fix</t>
+        </is>
+      </c>
+      <c r="D147" s="15" t="inlineStr">
+        <is>
+          <t>Payments</t>
+        </is>
+      </c>
+      <c r="E147" s="18" t="inlineStr">
+        <is>
+          <t>An out-of-order EXPIRATION could revoke a renewed subscriber</t>
+        </is>
+      </c>
+      <c r="F147" s="18" t="inlineStr">
+        <is>
+          <t>The webhook only de-duplicated by event id, and RevenueCat can redeliver out of order. Writes now apply only if the event is at least as new as the last applied one (event_timestamp_ms vs rc_last_event_at, checked in the UPDATE). Also, the ledger row was written before the profile update, so a delivery that 500'd was dropped as a duplicate on retry; it is now written after. Deployed 2026-10-01.</t>
+        </is>
+      </c>
+      <c r="G147" s="16" t="inlineStr">
+        <is>
+          <t>1.1.8</t>
+        </is>
+      </c>
+      <c r="H147" s="22" t="inlineStr">
+        <is>
+          <t>Edge deploy</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="40" customHeight="1">
+      <c r="A148" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B148" s="16" t="inlineStr">
+        <is>
+          <t>56843dd</t>
+        </is>
+      </c>
+      <c r="C148" s="19" t="inlineStr">
+        <is>
+          <t>Bug Fix</t>
+        </is>
+      </c>
+      <c r="D148" s="15" t="inlineStr">
+        <is>
+          <t>Codes</t>
+        </is>
+      </c>
+      <c r="E148" s="18" t="inlineStr">
+        <is>
+          <t>A class redeeming a study code on one school network was blocked after 20</t>
+        </is>
+      </c>
+      <c r="F148" s="18" t="inlineStr">
+        <is>
+          <t>The per-IP hourly limit counted successful redemptions as attempts. It now counts failed guesses only, which is what brute force produces. Deployed 2026-10-01.</t>
+        </is>
+      </c>
+      <c r="G148" s="16" t="inlineStr">
+        <is>
+          <t>1.1.8</t>
+        </is>
+      </c>
+      <c r="H148" s="22" t="inlineStr">
+        <is>
+          <t>Edge deploy</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="40" customHeight="1">
+      <c r="A149" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B149" s="16" t="inlineStr">
+        <is>
+          <t>56843dd</t>
+        </is>
+      </c>
+      <c r="C149" s="19" t="inlineStr">
+        <is>
+          <t>Bug Fix</t>
+        </is>
+      </c>
+      <c r="D149" s="15" t="inlineStr">
+        <is>
+          <t>Screen Time</t>
+        </is>
+      </c>
+      <c r="E149" s="18" t="inlineStr">
+        <is>
+          <t>Background shield blocked every app category for non-Pro users</t>
+        </is>
+      </c>
+      <c r="F149" s="18" t="inlineStr">
+        <is>
+          <t>The DriftMonitor extension forced .all categories for any non-Pro user when the balance ran out, while the in-app path had already moved to honouring the user's picks. The extension now matches: picks win, and .all is only the fallback when nothing is picked.</t>
+        </is>
+      </c>
+      <c r="G149" s="16" t="inlineStr">
+        <is>
+          <t>1.1.8</t>
+        </is>
+      </c>
+      <c r="H149" s="22" t="inlineStr">
+        <is>
+          <t>Native build</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="40" customHeight="1">
+      <c r="A150" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B150" s="16" t="inlineStr">
+        <is>
+          <t>56843dd</t>
+        </is>
+      </c>
+      <c r="C150" s="19" t="inlineStr">
+        <is>
+          <t>Bug Fix</t>
+        </is>
+      </c>
+      <c r="D150" s="15" t="inlineStr">
+        <is>
+          <t>Codes</t>
+        </is>
+      </c>
+      <c r="E150" s="18" t="inlineStr">
+        <is>
+          <t>Redeeming a dated code after a revoke restored permanent access</t>
+        </is>
+      </c>
+      <c r="F150" s="18" t="inlineStr">
+        <is>
+          <t>redeem_cohort_code's never-shorten rule treated a revoked grant (granted = false, expires_at null) as permanent, so any later 30-day code came back permanent with the old child seats. schema_v20 only honours an existing grant that is live. Migration written; not yet pushed.</t>
+        </is>
+      </c>
+      <c r="G150" s="16" t="inlineStr">
+        <is>
+          <t>1.1.8</t>
+        </is>
+      </c>
+      <c r="H150" s="22" t="inlineStr">
+        <is>
+          <t>SQL migration</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H145"/>
+  <autoFilter ref="A1:H150"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Drift-changelog.xlsx
+++ b/Drift-changelog.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Changes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Changes'!$A$1:$H$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Changes'!$A$1:$H$157</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -578,7 +578,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every feature, fix and change shipped. 2026-07-07 – 2026-10-01.</t>
+          <t>Every feature, fix and change shipped. 2026-07-07 – 2026-10-11.</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>COUNTA(Changes!E2:E150)</f>
+        <f>COUNTA(Changes!E2:E157)</f>
         <v/>
       </c>
     </row>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$150,A8)</f>
+        <f>COUNTIF(Changes!$C$2:$C$157,A8)</f>
         <v/>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="E8" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D8)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D8)</f>
         <v/>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="H8" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$150,G8)</f>
+        <f>COUNTIF(Changes!$G$2:$G$157,G8)</f>
         <v/>
       </c>
     </row>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$150,A9)</f>
+        <f>COUNTIF(Changes!$C$2:$C$157,A9)</f>
         <v/>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="E9" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D9)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D9)</f>
         <v/>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="H9" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$150,G9)</f>
+        <f>COUNTIF(Changes!$G$2:$G$157,G9)</f>
         <v/>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$150,A10)</f>
+        <f>COUNTIF(Changes!$C$2:$C$157,A10)</f>
         <v/>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="E10" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D10)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D10)</f>
         <v/>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="H10" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$150,G10)</f>
+        <f>COUNTIF(Changes!$G$2:$G$157,G10)</f>
         <v/>
       </c>
     </row>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$150,A11)</f>
+        <f>COUNTIF(Changes!$C$2:$C$157,A11)</f>
         <v/>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="E11" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D11)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D11)</f>
         <v/>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="H11" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$150,G11)</f>
+        <f>COUNTIF(Changes!$G$2:$G$157,G11)</f>
         <v/>
       </c>
     </row>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$150,A12)</f>
+        <f>COUNTIF(Changes!$C$2:$C$157,A12)</f>
         <v/>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="E12" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D12)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D12)</f>
         <v/>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="H12" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$150,G12)</f>
+        <f>COUNTIF(Changes!$G$2:$G$157,G12)</f>
         <v/>
       </c>
     </row>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$150,A13)</f>
+        <f>COUNTIF(Changes!$C$2:$C$157,A13)</f>
         <v/>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="E13" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D13)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D13)</f>
         <v/>
       </c>
       <c r="G13" s="7" t="inlineStr">
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="H13" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$150,G13)</f>
+        <f>COUNTIF(Changes!$G$2:$G$157,G13)</f>
         <v/>
       </c>
     </row>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$150,A14)</f>
+        <f>COUNTIF(Changes!$C$2:$C$157,A14)</f>
         <v/>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -832,16 +832,16 @@
         </is>
       </c>
       <c r="E14" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D14)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D14)</f>
         <v/>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Unreleased</t>
+          <t>1.2.0</t>
         </is>
       </c>
       <c r="H14" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$150,G14)</f>
+        <f>COUNTIF(Changes!$G$2:$G$157,G14)</f>
         <v/>
       </c>
     </row>
@@ -852,7 +852,16 @@
         </is>
       </c>
       <c r="E15" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D15)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D15)</f>
+        <v/>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Unreleased</t>
+        </is>
+      </c>
+      <c r="H15" s="7">
+        <f>COUNTIF(Changes!$G$2:$G$157,G15)</f>
         <v/>
       </c>
     </row>
@@ -863,7 +872,7 @@
         </is>
       </c>
       <c r="E16" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D16)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D16)</f>
         <v/>
       </c>
     </row>
@@ -874,7 +883,7 @@
         </is>
       </c>
       <c r="E17" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D17)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D17)</f>
         <v/>
       </c>
     </row>
@@ -885,7 +894,7 @@
         </is>
       </c>
       <c r="E18" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D18)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D18)</f>
         <v/>
       </c>
     </row>
@@ -896,7 +905,7 @@
         </is>
       </c>
       <c r="E19" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D19)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D19)</f>
         <v/>
       </c>
     </row>
@@ -907,7 +916,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D20)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D20)</f>
         <v/>
       </c>
     </row>
@@ -918,7 +927,7 @@
         </is>
       </c>
       <c r="E21" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D21)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D21)</f>
         <v/>
       </c>
     </row>
@@ -929,7 +938,7 @@
         </is>
       </c>
       <c r="E22" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D22)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D22)</f>
         <v/>
       </c>
     </row>
@@ -940,7 +949,7 @@
         </is>
       </c>
       <c r="E23" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D23)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D23)</f>
         <v/>
       </c>
     </row>
@@ -951,7 +960,7 @@
         </is>
       </c>
       <c r="E24" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D24)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D24)</f>
         <v/>
       </c>
     </row>
@@ -962,7 +971,7 @@
         </is>
       </c>
       <c r="E25" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D25)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D25)</f>
         <v/>
       </c>
     </row>
@@ -973,7 +982,7 @@
         </is>
       </c>
       <c r="E26" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D26)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D26)</f>
         <v/>
       </c>
     </row>
@@ -984,7 +993,7 @@
         </is>
       </c>
       <c r="E27" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D27)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D27)</f>
         <v/>
       </c>
     </row>
@@ -995,7 +1004,7 @@
         </is>
       </c>
       <c r="E28" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D28)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D28)</f>
         <v/>
       </c>
     </row>
@@ -1006,7 +1015,7 @@
         </is>
       </c>
       <c r="E29" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D29)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D29)</f>
         <v/>
       </c>
     </row>
@@ -1017,7 +1026,7 @@
         </is>
       </c>
       <c r="E30" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D30)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D30)</f>
         <v/>
       </c>
     </row>
@@ -1028,7 +1037,7 @@
         </is>
       </c>
       <c r="E31" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D31)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D31)</f>
         <v/>
       </c>
     </row>
@@ -1039,7 +1048,7 @@
         </is>
       </c>
       <c r="E32" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D32)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D32)</f>
         <v/>
       </c>
     </row>
@@ -1050,7 +1059,7 @@
         </is>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D33)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D33)</f>
         <v/>
       </c>
     </row>
@@ -1061,7 +1070,7 @@
         </is>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D34)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D34)</f>
         <v/>
       </c>
     </row>
@@ -1072,7 +1081,7 @@
         </is>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D35)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D35)</f>
         <v/>
       </c>
     </row>
@@ -1083,7 +1092,7 @@
         </is>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D36)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D36)</f>
         <v/>
       </c>
     </row>
@@ -1094,7 +1103,7 @@
         </is>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D37)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D37)</f>
         <v/>
       </c>
     </row>
@@ -1105,7 +1114,7 @@
         </is>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D38)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D38)</f>
         <v/>
       </c>
     </row>
@@ -1116,7 +1125,7 @@
         </is>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D39)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D39)</f>
         <v/>
       </c>
     </row>
@@ -1127,7 +1136,7 @@
         </is>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D40)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D40)</f>
         <v/>
       </c>
     </row>
@@ -1138,7 +1147,7 @@
         </is>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D41)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D41)</f>
         <v/>
       </c>
     </row>
@@ -1149,7 +1158,7 @@
         </is>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D42)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D42)</f>
         <v/>
       </c>
     </row>
@@ -1160,7 +1169,7 @@
         </is>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D43)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D43)</f>
         <v/>
       </c>
     </row>
@@ -1171,7 +1180,7 @@
         </is>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D44)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D44)</f>
         <v/>
       </c>
     </row>
@@ -1182,7 +1191,7 @@
         </is>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D45)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D45)</f>
         <v/>
       </c>
     </row>
@@ -1193,7 +1202,7 @@
         </is>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D46)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D46)</f>
         <v/>
       </c>
     </row>
@@ -1204,7 +1213,7 @@
         </is>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D47)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D47)</f>
         <v/>
       </c>
     </row>
@@ -1215,7 +1224,7 @@
         </is>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D48)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D48)</f>
         <v/>
       </c>
     </row>
@@ -1226,7 +1235,7 @@
         </is>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D49)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D49)</f>
         <v/>
       </c>
     </row>
@@ -1237,7 +1246,7 @@
         </is>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D50)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D50)</f>
         <v/>
       </c>
     </row>
@@ -1248,7 +1257,7 @@
         </is>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D51)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D51)</f>
         <v/>
       </c>
     </row>
@@ -1259,7 +1268,7 @@
         </is>
       </c>
       <c r="E52" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D52)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D52)</f>
         <v/>
       </c>
     </row>
@@ -1270,7 +1279,7 @@
         </is>
       </c>
       <c r="E53" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$150,D53)</f>
+        <f>COUNTIF(Changes!$D$2:$D$157,D53)</f>
         <v/>
       </c>
     </row>
@@ -1320,7 +1329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H150"/>
+  <dimension ref="A1:H157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7611,7 +7620,7 @@
       </c>
       <c r="F150" s="18" t="inlineStr">
         <is>
-          <t>redeem_cohort_code's never-shorten rule treated a revoked grant (granted = false, expires_at null) as permanent, so any later 30-day code came back permanent with the old child seats. schema_v20 only honours an existing grant that is live. Migration written; not yet pushed.</t>
+          <t>redeem_cohort_code's never-shorten rule treated a revoked grant (granted = false, expires_at null) as permanent, so any later 30-day code came back permanent with the old child seats. schema_v20 only honours an existing grant that is live. Applied (20261001000001 confirmed in the live migration history 2026-10-11).</t>
         </is>
       </c>
       <c r="G150" s="16" t="inlineStr">
@@ -7625,8 +7634,302 @@
         </is>
       </c>
     </row>
+    <row r="151" ht="40" customHeight="1">
+      <c r="A151" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B151" s="16" t="inlineStr">
+        <is>
+          <t>f06f1a2</t>
+        </is>
+      </c>
+      <c r="C151" s="17" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D151" s="15" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="E151" s="18" t="inlineStr">
+        <is>
+          <t>Free tier for personal accounts</t>
+        </is>
+      </c>
+      <c r="F151" s="18" t="inlineStr">
+        <is>
+          <t>The hard paywall turned away teens, who mostly can't start an App Store subscription without a parent's card. Free: up to 3 blocked apps/categories/sites, 3 photo-verified tasks a day (flat duration-based credits), plant stages 1-3, focus timer. Pro: unlimited picks and tasks, AI-valued credits, Lockbox, blocked hours, repeating tasks, stages 4+, challenges. Family stays a hard paywall. verify-task gives non-Pro callers app_config.free_daily_tasks approved checks since their local midnight, then 402 free_limit; is_pro() unchanged. Migration applied and verify-task deployed 2026-10-11, both verified live.</t>
+        </is>
+      </c>
+      <c r="G151" s="16" t="inlineStr">
+        <is>
+          <t>1.2.0</t>
+        </is>
+      </c>
+      <c r="H151" s="22" t="inlineStr">
+        <is>
+          <t>Native build, SQL migration, Edge deploy</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="40" customHeight="1">
+      <c r="A152" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B152" s="16" t="inlineStr">
+        <is>
+          <t>f06f1a2</t>
+        </is>
+      </c>
+      <c r="C152" s="17" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D152" s="15" t="inlineStr">
+        <is>
+          <t>Screen Time</t>
+        </is>
+      </c>
+      <c r="E152" s="18" t="inlineStr">
+        <is>
+          <t>App picker caps free users at 3 picks</t>
+        </is>
+      </c>
+      <c r="F152" s="18" t="inlineStr">
+        <is>
+          <t>Apple's picker has no selection limit and was bound straight to the saved selection, so every tap persisted (and was shielded) before anything could object. It now edits a draft: Done is disabled over the cap and Cancel keeps the old selection. Also fixes swipe-to-dismiss leaving the picker's promise unresolved.</t>
+        </is>
+      </c>
+      <c r="G152" s="16" t="inlineStr">
+        <is>
+          <t>1.2.0</t>
+        </is>
+      </c>
+      <c r="H152" s="22" t="inlineStr">
+        <is>
+          <t>Native build</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="40" customHeight="1">
+      <c r="A153" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B153" s="16" t="inlineStr">
+        <is>
+          <t>f06f1a2</t>
+        </is>
+      </c>
+      <c r="C153" s="17" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D153" s="15" t="inlineStr">
+        <is>
+          <t>Paywall</t>
+        </is>
+      </c>
+      <c r="E153" s="18" t="inlineStr">
+        <is>
+          <t>Pro upgrade sheet, and upgrade buttons that work</t>
+        </is>
+      </c>
+      <c r="F153" s="18" t="inlineStr">
+        <is>
+          <t>The paywall doubles as a closable Pro sheet for personal accounts. Every upgrade entry point (profile row, challenges, repeating tasks, AI info, picker limit) was a no-op; they now open it, as do the free-plan limits, Lockbox, blocked hours and the plant cap.</t>
+        </is>
+      </c>
+      <c r="G153" s="16" t="inlineStr">
+        <is>
+          <t>1.2.0</t>
+        </is>
+      </c>
+      <c r="H153" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="40" customHeight="1">
+      <c r="A154" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B154" s="16" t="inlineStr">
+        <is>
+          <t>f06f1a2</t>
+        </is>
+      </c>
+      <c r="C154" s="17" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D154" s="15" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E154" s="18" t="inlineStr">
+        <is>
+          <t>New users go straight to picking apps and the tour</t>
+        </is>
+      </c>
+      <c r="F154" s="18" t="inlineStr">
+        <is>
+          <t>The first-run sequence waited for proAccess, i.e. for a purchase. With the free tier it runs right after sign-up.</t>
+        </is>
+      </c>
+      <c r="G154" s="16" t="inlineStr">
+        <is>
+          <t>1.2.0</t>
+        </is>
+      </c>
+      <c r="H154" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="40" customHeight="1">
+      <c r="A155" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B155" s="16" t="inlineStr">
+        <is>
+          <t>f06f1a2</t>
+        </is>
+      </c>
+      <c r="C155" s="17" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D155" s="15" t="inlineStr">
+        <is>
+          <t>Reviews</t>
+        </is>
+      </c>
+      <c r="E155" s="18" t="inlineStr">
+        <is>
+          <t>Rating prompt after the first completed task and on reaching Sapling</t>
+        </is>
+      </c>
+      <c r="F155" s="18" t="inlineStr">
+        <is>
+          <t>Was after the third task only. The first earned unlock is the happiest moment in the app; onboarding never completes a task, so this stays clear of the 5.6.3 rejection. reviewPrompt.js still caps asks at 3 a year, 90 days apart.</t>
+        </is>
+      </c>
+      <c r="G155" s="16" t="inlineStr">
+        <is>
+          <t>1.2.0</t>
+        </is>
+      </c>
+      <c r="H155" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="40" customHeight="1">
+      <c r="A156" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B156" s="16" t="inlineStr">
+        <is>
+          <t>e82b13b</t>
+        </is>
+      </c>
+      <c r="C156" s="19" t="inlineStr">
+        <is>
+          <t>Bug Fix</t>
+        </is>
+      </c>
+      <c r="D156" s="15" t="inlineStr">
+        <is>
+          <t>Screen Time</t>
+        </is>
+      </c>
+      <c r="E156" s="18" t="inlineStr">
+        <is>
+          <t>Screen time drained while the phone was locked or idle</t>
+        </is>
+      </c>
+      <c r="F156" s="18" t="inlineStr">
+        <is>
+          <t>When iOS hadn't reported usage yet, Drift charged wall-clock time since it was last in the foreground, and a one-shot failsafe for balances under 15 minutes marked the whole balance spent at its deadline. Both billed a locked phone and time in unblocked apps. The DeviceActivityMonitor usage counter is now the only source of drain; the heartbeat and failsafe are gone. The visible balance can trail real use by one 5-15 minute checkpoint; the shield itself does not lag.</t>
+        </is>
+      </c>
+      <c r="G156" s="16" t="inlineStr">
+        <is>
+          <t>1.2.0</t>
+        </is>
+      </c>
+      <c r="H156" s="22" t="inlineStr">
+        <is>
+          <t>Native build</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="40" customHeight="1">
+      <c r="A157" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B157" s="16" t="inlineStr">
+        <is>
+          <t>f72e835</t>
+        </is>
+      </c>
+      <c r="C157" s="19" t="inlineStr">
+        <is>
+          <t>Bug Fix</t>
+        </is>
+      </c>
+      <c r="D157" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="E157" s="18" t="inlineStr">
+        <is>
+          <t>GitHub Pages site advertised $0.99/month after a 3-day trial</t>
+        </is>
+      </c>
+      <c r="F157" s="18" t="inlineStr">
+        <is>
+          <t>The docs/ pages were never updated when Pro was repriced to $4.99/$29.99 (0e7cd87). Six pages and the structured-data price now match driftproductivity.com. Live on Pages since 2026-10-11, independent of the app.</t>
+        </is>
+      </c>
+      <c r="G157" s="16" t="inlineStr">
+        <is>
+          <t>1.2.0</t>
+        </is>
+      </c>
+      <c r="H157" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H150"/>
+  <autoFilter ref="A1:H157"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Drift-changelog.xlsx
+++ b/Drift-changelog.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Changes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Changes'!$A$1:$H$157</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Changes'!$A$1:$H$158</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -578,7 +578,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every feature, fix and change shipped. 2026-07-07 – 2026-10-11.</t>
+          <t>Every feature, fix and change shipped. 2026-07-07 – 2026-10-12.</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>COUNTA(Changes!E2:E157)</f>
+        <f>COUNTA(Changes!E2:E158)</f>
         <v/>
       </c>
     </row>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$157,A8)</f>
+        <f>COUNTIF(Changes!$C$2:$C$158,A8)</f>
         <v/>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="E8" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D8)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D8)</f>
         <v/>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="H8" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$157,G8)</f>
+        <f>COUNTIF(Changes!$G$2:$G$158,G8)</f>
         <v/>
       </c>
     </row>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$157,A9)</f>
+        <f>COUNTIF(Changes!$C$2:$C$158,A9)</f>
         <v/>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="E9" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D9)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D9)</f>
         <v/>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="H9" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$157,G9)</f>
+        <f>COUNTIF(Changes!$G$2:$G$158,G9)</f>
         <v/>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$157,A10)</f>
+        <f>COUNTIF(Changes!$C$2:$C$158,A10)</f>
         <v/>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="E10" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D10)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D10)</f>
         <v/>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="H10" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$157,G10)</f>
+        <f>COUNTIF(Changes!$G$2:$G$158,G10)</f>
         <v/>
       </c>
     </row>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$157,A11)</f>
+        <f>COUNTIF(Changes!$C$2:$C$158,A11)</f>
         <v/>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="E11" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D11)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D11)</f>
         <v/>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="H11" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$157,G11)</f>
+        <f>COUNTIF(Changes!$G$2:$G$158,G11)</f>
         <v/>
       </c>
     </row>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$157,A12)</f>
+        <f>COUNTIF(Changes!$C$2:$C$158,A12)</f>
         <v/>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="E12" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D12)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D12)</f>
         <v/>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="H12" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$157,G12)</f>
+        <f>COUNTIF(Changes!$G$2:$G$158,G12)</f>
         <v/>
       </c>
     </row>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$157,A13)</f>
+        <f>COUNTIF(Changes!$C$2:$C$158,A13)</f>
         <v/>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="E13" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D13)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D13)</f>
         <v/>
       </c>
       <c r="G13" s="7" t="inlineStr">
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="H13" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$157,G13)</f>
+        <f>COUNTIF(Changes!$G$2:$G$158,G13)</f>
         <v/>
       </c>
     </row>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$157,A14)</f>
+        <f>COUNTIF(Changes!$C$2:$C$158,A14)</f>
         <v/>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="E14" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D14)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D14)</f>
         <v/>
       </c>
       <c r="G14" s="7" t="inlineStr">
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="H14" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$157,G14)</f>
+        <f>COUNTIF(Changes!$G$2:$G$158,G14)</f>
         <v/>
       </c>
     </row>
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="E15" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D15)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D15)</f>
         <v/>
       </c>
       <c r="G15" s="7" t="inlineStr">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="H15" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$157,G15)</f>
+        <f>COUNTIF(Changes!$G$2:$G$158,G15)</f>
         <v/>
       </c>
     </row>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="E16" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D16)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D16)</f>
         <v/>
       </c>
     </row>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="E17" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D17)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D17)</f>
         <v/>
       </c>
     </row>
@@ -894,7 +894,7 @@
         </is>
       </c>
       <c r="E18" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D18)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D18)</f>
         <v/>
       </c>
     </row>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="E19" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D19)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D19)</f>
         <v/>
       </c>
     </row>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D20)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D20)</f>
         <v/>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="E21" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D21)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D21)</f>
         <v/>
       </c>
     </row>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="E22" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D22)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D22)</f>
         <v/>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="E23" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D23)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D23)</f>
         <v/>
       </c>
     </row>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="E24" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D24)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D24)</f>
         <v/>
       </c>
     </row>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="E25" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D25)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D25)</f>
         <v/>
       </c>
     </row>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="E26" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D26)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D26)</f>
         <v/>
       </c>
     </row>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="E27" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D27)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D27)</f>
         <v/>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="E28" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D28)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D28)</f>
         <v/>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="E29" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D29)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D29)</f>
         <v/>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="E30" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D30)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D30)</f>
         <v/>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="E31" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D31)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D31)</f>
         <v/>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="E32" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D32)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D32)</f>
         <v/>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D33)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D33)</f>
         <v/>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D34)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D34)</f>
         <v/>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D35)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D35)</f>
         <v/>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D36)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D36)</f>
         <v/>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D37)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D37)</f>
         <v/>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D38)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D38)</f>
         <v/>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D39)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D39)</f>
         <v/>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D40)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D40)</f>
         <v/>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D41)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D41)</f>
         <v/>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
         </is>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D42)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D42)</f>
         <v/>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D43)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D43)</f>
         <v/>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D44)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D44)</f>
         <v/>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D45)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D45)</f>
         <v/>
       </c>
     </row>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D46)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D46)</f>
         <v/>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D47)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D47)</f>
         <v/>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D48)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D48)</f>
         <v/>
       </c>
     </row>
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D49)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D49)</f>
         <v/>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D50)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D50)</f>
         <v/>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D51)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D51)</f>
         <v/>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="E52" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D52)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D52)</f>
         <v/>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="E53" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$157,D53)</f>
+        <f>COUNTIF(Changes!$D$2:$D$158,D53)</f>
         <v/>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H157"/>
+  <dimension ref="A1:H158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7928,8 +7928,50 @@
         </is>
       </c>
     </row>
+    <row r="158" ht="40" customHeight="1">
+      <c r="A158" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B158" s="16" t="inlineStr">
+        <is>
+          <t>90dc57e</t>
+        </is>
+      </c>
+      <c r="C158" s="17" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D158" s="15" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="E158" s="18" t="inlineStr">
+        <is>
+          <t>Loyalty pricing: monthly Pro drops 50¢ every 2 months, down to $2.99</t>
+        </is>
+      </c>
+      <c r="F158" s="18" t="inlineStr">
+        <is>
+          <t>$4.99 for months 0-1, then $4.49, $3.99, $3.49 and $2.99 from month 8, counted over an unbroken paid run (trial days excluded). Unsubscribing or lapsing resets it. Apple won't let an app change one subscriber's price, so each step is a promotional offer on com.drift.pro.month (loyalty_449/399/349 for 2 months, loyalty_299 for 12) that the subscriber confirms once; it starts at their next renewal. The webhook keeps profiles.sub_paid_since (guarded like the other subscription columns). Ships switched off: needs schema_v22 pushed, the webhook deployed, the four offers in App Store Connect, the subscription key in RevenueCat, then app_config.loyalty_pricing = 'true'.</t>
+        </is>
+      </c>
+      <c r="G158" s="16" t="inlineStr">
+        <is>
+          <t>1.2.0</t>
+        </is>
+      </c>
+      <c r="H158" s="22" t="inlineStr">
+        <is>
+          <t>SQL migration, Edge deploy, App Store Connect</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H157"/>
+  <autoFilter ref="A1:H158"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Drift-changelog.xlsx
+++ b/Drift-changelog.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Changes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Changes'!$A$1:$H$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Changes'!$A$1:$H$159</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>COUNTA(Changes!E2:E158)</f>
+        <f>COUNTA(Changes!E2:E159)</f>
         <v/>
       </c>
     </row>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$158,A8)</f>
+        <f>COUNTIF(Changes!$C$2:$C$159,A8)</f>
         <v/>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="E8" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D8)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D8)</f>
         <v/>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="H8" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$158,G8)</f>
+        <f>COUNTIF(Changes!$G$2:$G$159,G8)</f>
         <v/>
       </c>
     </row>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$158,A9)</f>
+        <f>COUNTIF(Changes!$C$2:$C$159,A9)</f>
         <v/>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="E9" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D9)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D9)</f>
         <v/>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="H9" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$158,G9)</f>
+        <f>COUNTIF(Changes!$G$2:$G$159,G9)</f>
         <v/>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$158,A10)</f>
+        <f>COUNTIF(Changes!$C$2:$C$159,A10)</f>
         <v/>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="E10" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D10)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D10)</f>
         <v/>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="H10" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$158,G10)</f>
+        <f>COUNTIF(Changes!$G$2:$G$159,G10)</f>
         <v/>
       </c>
     </row>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$158,A11)</f>
+        <f>COUNTIF(Changes!$C$2:$C$159,A11)</f>
         <v/>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="E11" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D11)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D11)</f>
         <v/>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="H11" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$158,G11)</f>
+        <f>COUNTIF(Changes!$G$2:$G$159,G11)</f>
         <v/>
       </c>
     </row>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$158,A12)</f>
+        <f>COUNTIF(Changes!$C$2:$C$159,A12)</f>
         <v/>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="E12" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D12)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D12)</f>
         <v/>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="H12" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$158,G12)</f>
+        <f>COUNTIF(Changes!$G$2:$G$159,G12)</f>
         <v/>
       </c>
     </row>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$158,A13)</f>
+        <f>COUNTIF(Changes!$C$2:$C$159,A13)</f>
         <v/>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="E13" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D13)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D13)</f>
         <v/>
       </c>
       <c r="G13" s="7" t="inlineStr">
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="H13" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$158,G13)</f>
+        <f>COUNTIF(Changes!$G$2:$G$159,G13)</f>
         <v/>
       </c>
     </row>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$158,A14)</f>
+        <f>COUNTIF(Changes!$C$2:$C$159,A14)</f>
         <v/>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="E14" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D14)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D14)</f>
         <v/>
       </c>
       <c r="G14" s="7" t="inlineStr">
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="H14" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$158,G14)</f>
+        <f>COUNTIF(Changes!$G$2:$G$159,G14)</f>
         <v/>
       </c>
     </row>
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="E15" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D15)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D15)</f>
         <v/>
       </c>
       <c r="G15" s="7" t="inlineStr">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="H15" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$158,G15)</f>
+        <f>COUNTIF(Changes!$G$2:$G$159,G15)</f>
         <v/>
       </c>
     </row>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="E16" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D16)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D16)</f>
         <v/>
       </c>
     </row>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="E17" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D17)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D17)</f>
         <v/>
       </c>
     </row>
@@ -894,7 +894,7 @@
         </is>
       </c>
       <c r="E18" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D18)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D18)</f>
         <v/>
       </c>
     </row>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="E19" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D19)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D19)</f>
         <v/>
       </c>
     </row>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D20)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D20)</f>
         <v/>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="E21" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D21)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D21)</f>
         <v/>
       </c>
     </row>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="E22" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D22)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D22)</f>
         <v/>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="E23" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D23)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D23)</f>
         <v/>
       </c>
     </row>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="E24" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D24)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D24)</f>
         <v/>
       </c>
     </row>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="E25" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D25)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D25)</f>
         <v/>
       </c>
     </row>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="E26" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D26)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D26)</f>
         <v/>
       </c>
     </row>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="E27" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D27)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D27)</f>
         <v/>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="E28" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D28)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D28)</f>
         <v/>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="E29" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D29)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D29)</f>
         <v/>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="E30" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D30)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D30)</f>
         <v/>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="E31" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D31)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D31)</f>
         <v/>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="E32" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D32)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D32)</f>
         <v/>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D33)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D33)</f>
         <v/>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D34)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D34)</f>
         <v/>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D35)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D35)</f>
         <v/>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D36)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D36)</f>
         <v/>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D37)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D37)</f>
         <v/>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D38)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D38)</f>
         <v/>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D39)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D39)</f>
         <v/>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D40)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D40)</f>
         <v/>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D41)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D41)</f>
         <v/>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
         </is>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D42)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D42)</f>
         <v/>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D43)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D43)</f>
         <v/>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D44)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D44)</f>
         <v/>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D45)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D45)</f>
         <v/>
       </c>
     </row>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D46)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D46)</f>
         <v/>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D47)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D47)</f>
         <v/>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D48)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D48)</f>
         <v/>
       </c>
     </row>
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D49)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D49)</f>
         <v/>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D50)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D50)</f>
         <v/>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D51)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D51)</f>
         <v/>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="E52" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D52)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D52)</f>
         <v/>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="E53" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$158,D53)</f>
+        <f>COUNTIF(Changes!$D$2:$D$159,D53)</f>
         <v/>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H158"/>
+  <dimension ref="A1:H159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7970,8 +7970,50 @@
         </is>
       </c>
     </row>
+    <row r="159" ht="40" customHeight="1">
+      <c r="A159" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B159" s="16" t="inlineStr">
+        <is>
+          <t>36aef9e</t>
+        </is>
+      </c>
+      <c r="C159" s="23" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D159" s="15" t="inlineStr">
+        <is>
+          <t>Paywall</t>
+        </is>
+      </c>
+      <c r="E159" s="18" t="inlineStr">
+        <is>
+          <t>Simpler Pro sheet, and it shows loyalty pricing</t>
+        </is>
+      </c>
+      <c r="F159" s="18" t="inlineStr">
+        <is>
+          <t>Down to a name, one line on what Pro adds, two plan rows and one button (trial on the button), from a two-line headline, four bullets and tiles. Monthly reads 'Your price drops every 2 months you stay, down to $2.99/mo' using Apple's localized floor price, only while loyalty_pricing is on and the offer exists; the terms add that each lower price is offered in the app to accept. Apple 3.1.2 items unchanged.</t>
+        </is>
+      </c>
+      <c r="G159" s="16" t="inlineStr">
+        <is>
+          <t>1.2.0</t>
+        </is>
+      </c>
+      <c r="H159" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H158"/>
+  <autoFilter ref="A1:H159"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Drift-changelog.xlsx
+++ b/Drift-changelog.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Changes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Changes'!$A$1:$H$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Changes'!$A$1:$H$164</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -578,7 +578,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every feature, fix and change shipped. 2026-07-07 – 2026-10-12.</t>
+          <t>Every feature, fix and change shipped. 2026-07-07 – 2026-10-26.</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>COUNTA(Changes!E2:E159)</f>
+        <f>COUNTA(Changes!E2:E164)</f>
         <v/>
       </c>
     </row>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$159,A8)</f>
+        <f>COUNTIF(Changes!$C$2:$C$164,A8)</f>
         <v/>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="E8" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D8)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D8)</f>
         <v/>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="H8" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$159,G8)</f>
+        <f>COUNTIF(Changes!$G$2:$G$164,G8)</f>
         <v/>
       </c>
     </row>
@@ -678,16 +678,16 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$159,A9)</f>
+        <f>COUNTIF(Changes!$C$2:$C$164,A9)</f>
         <v/>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Action Plan</t>
+          <t>Account</t>
         </is>
       </c>
       <c r="E9" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D9)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D9)</f>
         <v/>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="H9" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$159,G9)</f>
+        <f>COUNTIF(Changes!$G$2:$G$164,G9)</f>
         <v/>
       </c>
     </row>
@@ -707,16 +707,16 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$159,A10)</f>
+        <f>COUNTIF(Changes!$C$2:$C$164,A10)</f>
         <v/>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Add Task</t>
+          <t>Action Plan</t>
         </is>
       </c>
       <c r="E10" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D10)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D10)</f>
         <v/>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="H10" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$159,G10)</f>
+        <f>COUNTIF(Changes!$G$2:$G$164,G10)</f>
         <v/>
       </c>
     </row>
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$159,A11)</f>
+        <f>COUNTIF(Changes!$C$2:$C$164,A11)</f>
         <v/>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Add Task</t>
         </is>
       </c>
       <c r="E11" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D11)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D11)</f>
         <v/>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="H11" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$159,G11)</f>
+        <f>COUNTIF(Changes!$G$2:$G$164,G11)</f>
         <v/>
       </c>
     </row>
@@ -765,16 +765,16 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$159,A12)</f>
+        <f>COUNTIF(Changes!$C$2:$C$164,A12)</f>
         <v/>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Auth</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="E12" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D12)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D12)</f>
         <v/>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="H12" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$159,G12)</f>
+        <f>COUNTIF(Changes!$G$2:$G$164,G12)</f>
         <v/>
       </c>
     </row>
@@ -794,16 +794,16 @@
         </is>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$159,A13)</f>
+        <f>COUNTIF(Changes!$C$2:$C$164,A13)</f>
         <v/>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Auth / Sync</t>
+          <t>Auth</t>
         </is>
       </c>
       <c r="E13" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D13)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D13)</f>
         <v/>
       </c>
       <c r="G13" s="7" t="inlineStr">
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="H13" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$159,G13)</f>
+        <f>COUNTIF(Changes!$G$2:$G$164,G13)</f>
         <v/>
       </c>
     </row>
@@ -823,16 +823,16 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>COUNTIF(Changes!$C$2:$C$159,A14)</f>
+        <f>COUNTIF(Changes!$C$2:$C$164,A14)</f>
         <v/>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Auth / Sync</t>
         </is>
       </c>
       <c r="E14" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D14)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D14)</f>
         <v/>
       </c>
       <c r="G14" s="7" t="inlineStr">
@@ -841,478 +841,513 @@
         </is>
       </c>
       <c r="H14" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$159,G14)</f>
+        <f>COUNTIF(Changes!$G$2:$G$164,G14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Billing</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="E15" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D15)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D15)</f>
         <v/>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Unreleased</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="H15" s="7">
-        <f>COUNTIF(Changes!$G$2:$G$159,G15)</f>
+        <f>COUNTIF(Changes!$G$2:$G$164,G15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>CI/CD</t>
+          <t>Billing</t>
         </is>
       </c>
       <c r="E16" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D16)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D16)</f>
+        <v/>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Unreleased</t>
+        </is>
+      </c>
+      <c r="H16" s="7">
+        <f>COUNTIF(Changes!$G$2:$G$164,G16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>CI/CD</t>
         </is>
       </c>
       <c r="E17" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D17)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Challenges</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E18" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D18)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Codes</t>
+          <t>Challenges</t>
         </is>
       </c>
       <c r="E19" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D19)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Cohort codes</t>
+          <t>Codes</t>
         </is>
       </c>
       <c r="E20" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D20)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Dependencies</t>
+          <t>Cohort codes</t>
         </is>
       </c>
       <c r="E21" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D21)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Dev</t>
+          <t>Dependencies</t>
         </is>
       </c>
       <c r="E22" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D22)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Discoverability</t>
+          <t>Dev</t>
         </is>
       </c>
       <c r="E23" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D23)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D23)</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Drift In</t>
+          <t>Discoverability</t>
         </is>
       </c>
       <c r="E24" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D24)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>Drift In</t>
         </is>
       </c>
       <c r="E25" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D25)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>Entitlement</t>
         </is>
       </c>
       <c r="E26" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D26)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Force update</t>
+          <t>Family</t>
         </is>
       </c>
       <c r="E27" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D27)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D27)</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Force update</t>
         </is>
       </c>
       <c r="E28" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D28)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Interaction</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="E29" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D29)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Lab</t>
+          <t>Interaction</t>
         </is>
       </c>
       <c r="E30" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D30)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Live Activity</t>
+          <t>Lab</t>
         </is>
       </c>
       <c r="E31" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D31)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Lockbox</t>
+          <t>Live Activity</t>
         </is>
       </c>
       <c r="E32" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D32)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Navigation</t>
+          <t>Lockbox</t>
         </is>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D33)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Navigation</t>
         </is>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D34)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D34)</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D35)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D35)</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Payments</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D36)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D36)</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Paywall</t>
+          <t>Payments</t>
         </is>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D37)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D37)</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Paywall</t>
         </is>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D38)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D38)</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D39)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D39)</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Privacy</t>
         </is>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D40)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D40)</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Release</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D41)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D41)</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D42)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D42)</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Scaling</t>
+          <t>Release</t>
         </is>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D43)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D43)</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Screen Time</t>
+          <t>Reviews</t>
         </is>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D44)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D44)</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Scaling</t>
         </is>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D45)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D45)</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Siri</t>
+          <t>Screen Time</t>
         </is>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D46)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D46)</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Sleep Guard</t>
+          <t>Shield</t>
         </is>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D47)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D47)</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Social</t>
+          <t>Siri</t>
         </is>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D48)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D48)</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Tasks</t>
+          <t>Sleep Guard</t>
         </is>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D49)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D49)</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Theme</t>
+          <t>Social</t>
         </is>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D50)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D50)</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Tour</t>
+          <t>Tasks</t>
         </is>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D51)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D51)</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Theme</t>
         </is>
       </c>
       <c r="E52" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D52)</f>
+        <f>COUNTIF(Changes!$D$2:$D$164,D52)</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="D53" s="7" t="inlineStr">
         <is>
+          <t>Tour</t>
+        </is>
+      </c>
+      <c r="E53" s="7">
+        <f>COUNTIF(Changes!$D$2:$D$164,D53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="E54" s="7">
+        <f>COUNTIF(Changes!$D$2:$D$164,D54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="D55" s="7" t="inlineStr">
+        <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="E53" s="7">
-        <f>COUNTIF(Changes!$D$2:$D$159,D53)</f>
+      <c r="E55" s="7">
+        <f>COUNTIF(Changes!$D$2:$D$164,D55)</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>i18n</t>
+        </is>
+      </c>
+      <c r="E56" s="7">
+        <f>COUNTIF(Changes!$D$2:$D$164,D56)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="13" t="inlineStr">
-        <is>
-          <t>• 1.1.8 is the last version submitted to the App Store. Everything marked Unreleased is on main but not shipped.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="13" t="inlineStr">
-        <is>
-          <t>• "Needs" says what a change requires beyond a normal JS reload: a native rebuild, an edge-function deploy, or SQL run in Supabase.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="13" t="inlineStr">
-        <is>
-          <t>• Native-build items are currently blocked on Apple Developer account access, so they are not device-tested.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
+        <is>
+          <t>• 1.2.0 is the version live on the App Store; 1.3.0 is the next submission. Everything marked Unreleased is on main but not shipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="13" t="inlineStr">
+        <is>
+          <t>• "Needs" says what a change requires beyond a normal JS reload: a native rebuild, an edge-function deploy, or SQL run in Supabase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="13" t="inlineStr">
         <is>
           <t>• Counts on this sheet are formulas over the Changes tab — they update if you edit, add or delete rows there.</t>
         </is>
@@ -1329,7 +1364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H159"/>
+  <dimension ref="A1:H164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8012,8 +8047,218 @@
         </is>
       </c>
     </row>
+    <row r="160" ht="40" customHeight="1">
+      <c r="A160" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B160" s="16" t="inlineStr">
+        <is>
+          <t>cf38bc0</t>
+        </is>
+      </c>
+      <c r="C160" s="17" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D160" s="15" t="inlineStr">
+        <is>
+          <t>i18n</t>
+        </is>
+      </c>
+      <c r="E160" s="18" t="inlineStr">
+        <is>
+          <t>App available in 20 languages</t>
+        </is>
+      </c>
+      <c r="F160" s="18" t="inlineStr">
+        <is>
+          <t>English plus Simplified/Traditional Chinese, Hindi, Spanish, French, Arabic, Portuguese, Russian, Indonesian, German, Japanese, Turkish, Vietnamese, Korean, Italian, Polish, Ukrainian, Thai and Dutch. English-as-key tr() with lazy-loaded catalogs; follows the device language or a picker in Profile (switching reloads the JS). Push notifications, AI feedback, the Screen Time shield/widgets and iOS permission prompts are translated too. Machine-authored translations, not reviewed by native speakers. Arabic text is translated but the layout is not mirrored.</t>
+        </is>
+      </c>
+      <c r="G160" s="16" t="inlineStr">
+        <is>
+          <t>1.3.0</t>
+        </is>
+      </c>
+      <c r="H160" s="22" t="inlineStr">
+        <is>
+          <t>Native build, Edge deploy</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="40" customHeight="1">
+      <c r="A161" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B161" s="16" t="inlineStr">
+        <is>
+          <t>cf38bc0</t>
+        </is>
+      </c>
+      <c r="C161" s="24" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D161" s="15" t="inlineStr">
+        <is>
+          <t>Privacy</t>
+        </is>
+      </c>
+      <c r="E161" s="18" t="inlineStr">
+        <is>
+          <t>Parental consent before a child can join a family</t>
+        </is>
+      </c>
+      <c r="F161" s="18" t="inlineStr">
+        <is>
+          <t>COPPA needs verifiable parental consent before collecting data from under-13s. Parents now see a direct notice (what is collected, who sees it, retention, rights) and consent; the Drift Family purchase is the verification method. join-family refuses a code until the family has consented (deploy join-family only once 1.3.0 is live, or current-version families can't add children). Parents can view, delete per child, or withdraw consent (erases every child). Consent is versioned and logged in parental_consent_events.</t>
+        </is>
+      </c>
+      <c r="G161" s="16" t="inlineStr">
+        <is>
+          <t>1.3.0</t>
+        </is>
+      </c>
+      <c r="H161" s="22" t="inlineStr">
+        <is>
+          <t>SQL migration, Edge deploy</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="40" customHeight="1">
+      <c r="A162" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B162" s="16" t="inlineStr">
+        <is>
+          <t>cf38bc0</t>
+        </is>
+      </c>
+      <c r="C162" s="19" t="inlineStr">
+        <is>
+          <t>Bug Fix</t>
+        </is>
+      </c>
+      <c r="D162" s="15" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="E162" s="18" t="inlineStr">
+        <is>
+          <t>Deleting an account left most of its data behind</t>
+        </is>
+      </c>
+      <c r="F162" s="18" t="inlineStr">
+        <is>
+          <t>delete-account called .delete() on tables guarded by prevent_hard_delete(), which raised, and the errors were swallowed, so tasks, ledger, analytics etc. survived. erase_account() (service-role only) now erases every user table under a transaction-local drift.erasure flag, scrubs the profile, and erases a parent's children too. Also revokes the Sign in with Apple token (Apple requires it; needs the APPLE_* secrets). Migration applied 2026-10-26 and verified live.</t>
+        </is>
+      </c>
+      <c r="G162" s="16" t="inlineStr">
+        <is>
+          <t>1.3.0</t>
+        </is>
+      </c>
+      <c r="H162" s="22" t="inlineStr">
+        <is>
+          <t>SQL migration, Edge deploy</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="40" customHeight="1">
+      <c r="A163" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B163" s="16" t="inlineStr">
+        <is>
+          <t>cf38bc0</t>
+        </is>
+      </c>
+      <c r="C163" s="24" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D163" s="15" t="inlineStr">
+        <is>
+          <t>Privacy</t>
+        </is>
+      </c>
+      <c r="E163" s="18" t="inlineStr">
+        <is>
+          <t>Children kept out of AI checks and analytics; retention purge</t>
+        </is>
+      </c>
+      <c r="F163" s="18" t="inlineStr">
+        <is>
+          <t>verify-task and evaluate-task reject child accounts, so nothing a child does reaches OpenAI; child analytics are disabled client-side, refused by RLS, and existing rows deleted. purge_expired_data() runs nightly via pg_cron (analytics 13 months, AI usage 90 days, push tokens 9 months, inactive child accounts 18 months). Neutral age gate at sign-up: 13+ for personal, 18+ for parent.</t>
+        </is>
+      </c>
+      <c r="G163" s="16" t="inlineStr">
+        <is>
+          <t>1.3.0</t>
+        </is>
+      </c>
+      <c r="H163" s="22" t="inlineStr">
+        <is>
+          <t>SQL migration, Edge deploy</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="40" customHeight="1">
+      <c r="A164" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B164" s="16" t="inlineStr">
+        <is>
+          <t>cf38bc0</t>
+        </is>
+      </c>
+      <c r="C164" s="21" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="D164" s="15" t="inlineStr">
+        <is>
+          <t>Privacy</t>
+        </is>
+      </c>
+      <c r="E164" s="18" t="inlineStr">
+        <is>
+          <t>Privacy policy rewritten to match what the app does</t>
+        </is>
+      </c>
+      <c r="F164" s="18" t="inlineStr">
+        <is>
+          <t>The old policy omitted data the app collects and named a processor it no longer uses. New one lists every data type and provider, a children's section, a retention table, CCPA/GDPR/consumer-health-data rights. Plus SECURITY_PROGRAM.md (the written security program COPPA requires).</t>
+        </is>
+      </c>
+      <c r="G164" s="16" t="inlineStr">
+        <is>
+          <t>1.3.0</t>
+        </is>
+      </c>
+      <c r="H164" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H159"/>
+  <autoFilter ref="A1:H164"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>